--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,5909 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132723979</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>870312</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7311654</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132724032</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>870091</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7311673</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132723966</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>870207</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7311650</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132723950</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>870220</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7311651</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132724035</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>870226</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7311649</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132723960</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92638</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>67</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>870208</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7311661</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132724008</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>870160</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7311638</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132723968</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>870266</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7311659</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132724048</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>870221</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7311646</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132724013</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>870190</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7311676</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132724009</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>870145</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7311659</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132723938</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>870177</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7311649</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132723962</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>870045</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7311671</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132724030</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>870251</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7311687</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132723949</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>870194</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7311657</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132724029</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>870105</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7311661</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>5 dm2.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132723947</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>870140</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7311665</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132724046</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93234</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>870273</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7311688</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp men enbart gran runt om.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132723969</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>870248</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7311673</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132724031</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>870082</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7311662</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132724012</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>870112</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7311656</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132723986</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>870063</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7311665</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132723951</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>870232</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7311643</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132723942</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>870192</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7311681</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132723980</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>870050</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7311668</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132724026</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>870175</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7311661</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132724024</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>870184</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7311672</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132723948</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>870106</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7311660</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132724015</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>870248</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7311676</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132724023</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>870206</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7311679</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132723958</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92638</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>67</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>870140</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7311665</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132723984</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99154</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>870326</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7311673</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132724042</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>870261</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7311655</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132723946</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>870305</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7311691</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132724043</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>870268</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7311645</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132723941</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>870223</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7311680</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132723985</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>870161</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7311671</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132723977</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>870291</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7311643</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132723940</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>870139</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7311657</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132723943</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>870194</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7311676</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132724033</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>870089</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7311673</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132723957</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>870341</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7311668</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132723963</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>870057</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7311663</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132724020</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>870092</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7311665</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132723964</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>870194</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7311653</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132724010</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>870185</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7311680</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132723959</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92638</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>67</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>870212</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7311654</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gren på granlåga.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132724019</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>870221</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7311678</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132723954</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92633</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>870345</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7311658</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132723983</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99154</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>870255</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7311639</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132724027</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>870230</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7311672</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132724021</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>870163</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7311664</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132724022</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>870153</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7311648</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132724011</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>870148</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7311649</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132723939</v>
+      </c>
+      <c r="B57" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>870106</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7311664</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132723952</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>870242</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7311674</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132724016</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>870243</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7311678</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132724028</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>870101</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7311647</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>5 dm2</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132724017</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>870091</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7311660</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132723979</v>
+        <v>132724032</v>
       </c>
       <c r="B3" t="n">
-        <v>97989</v>
+        <v>99119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870312</v>
+        <v>870091</v>
       </c>
       <c r="R3" t="n">
-        <v>7311654</v>
+        <v>7311673</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132724032</v>
+        <v>132723979</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>97990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870091</v>
+        <v>870312</v>
       </c>
       <c r="R4" t="n">
-        <v>7311673</v>
+        <v>7311654</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +984,7 @@
         <v>132723966</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132723950</v>
+        <v>132724035</v>
       </c>
       <c r="B6" t="n">
-        <v>91872</v>
+        <v>57133</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>870220</v>
+        <v>870226</v>
       </c>
       <c r="R6" t="n">
-        <v>7311651</v>
+        <v>7311649</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132724035</v>
+        <v>132723950</v>
       </c>
       <c r="B7" t="n">
-        <v>57132</v>
+        <v>91873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870226</v>
+        <v>870220</v>
       </c>
       <c r="R7" t="n">
-        <v>7311649</v>
+        <v>7311651</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132723960</v>
+        <v>132724008</v>
       </c>
       <c r="B8" t="n">
-        <v>92638</v>
+        <v>99119</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,34 +1283,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>870208</v>
+        <v>870160</v>
       </c>
       <c r="R8" t="n">
-        <v>7311661</v>
+        <v>7311638</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1351,6 +1355,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1369,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132724008</v>
+        <v>132723960</v>
       </c>
       <c r="B9" t="n">
-        <v>99119</v>
+        <v>92638</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,38 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>870160</v>
+        <v>870208</v>
       </c>
       <c r="R9" t="n">
-        <v>7311638</v>
+        <v>7311661</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1452,7 +1453,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132723968</v>
+        <v>132724048</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>78731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>870266</v>
+        <v>870221</v>
       </c>
       <c r="R10" t="n">
-        <v>7311659</v>
+        <v>7311646</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1544,14 +1544,35 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1568,45 +1589,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132724048</v>
+        <v>132724009</v>
       </c>
       <c r="B11" t="n">
-        <v>78730</v>
+        <v>99119</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>870221</v>
+        <v>870145</v>
       </c>
       <c r="R11" t="n">
-        <v>7311646</v>
+        <v>7311659</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1641,11 +1666,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1655,21 +1675,6 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1686,49 +1691,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132724013</v>
+        <v>132723968</v>
       </c>
       <c r="B12" t="n">
-        <v>99119</v>
+        <v>57951</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>870190</v>
+        <v>870266</v>
       </c>
       <c r="R12" t="n">
-        <v>7311676</v>
+        <v>7311659</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1769,7 +1770,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132724009</v>
+        <v>132724013</v>
       </c>
       <c r="B13" t="n">
         <v>99119</v>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>49</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>870145</v>
+        <v>870190</v>
       </c>
       <c r="R13" t="n">
-        <v>7311659</v>
+        <v>7311676</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1893,7 +1893,7 @@
         <v>132723938</v>
       </c>
       <c r="B14" t="n">
-        <v>106229</v>
+        <v>106230</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1987,45 +1987,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132723962</v>
+        <v>132724030</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>99119</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>870045</v>
+        <v>870251</v>
       </c>
       <c r="R15" t="n">
-        <v>7311671</v>
+        <v>7311687</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2066,6 +2070,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2084,49 +2089,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132724030</v>
+        <v>132723962</v>
       </c>
       <c r="B16" t="n">
-        <v>99119</v>
+        <v>57951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>870251</v>
+        <v>870045</v>
       </c>
       <c r="R16" t="n">
-        <v>7311687</v>
+        <v>7311671</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2167,7 +2168,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132723949</v>
+        <v>132723947</v>
       </c>
       <c r="B17" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>870194</v>
+        <v>870140</v>
       </c>
       <c r="R17" t="n">
-        <v>7311657</v>
+        <v>7311665</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2283,32 +2283,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132724029</v>
+        <v>132723949</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>91873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>870105</v>
+        <v>870194</v>
       </c>
       <c r="R18" t="n">
-        <v>7311661</v>
+        <v>7311657</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2356,18 +2356,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>5 dm2.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2386,32 +2380,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132723947</v>
+        <v>132724029</v>
       </c>
       <c r="B19" t="n">
-        <v>91872</v>
+        <v>99119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2421,10 +2415,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>870140</v>
+        <v>870105</v>
       </c>
       <c r="R19" t="n">
-        <v>7311665</v>
+        <v>7311661</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2459,12 +2453,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>5 dm2.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>132723969</v>
       </c>
       <c r="B21" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132724031</v>
+        <v>132724012</v>
       </c>
       <c r="B22" t="n">
         <v>99119</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>51</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>870082</v>
+        <v>870112</v>
       </c>
       <c r="R22" t="n">
-        <v>7311662</v>
+        <v>7311656</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132724012</v>
+        <v>132724031</v>
       </c>
       <c r="B23" t="n">
         <v>99119</v>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>870112</v>
+        <v>870082</v>
       </c>
       <c r="R23" t="n">
-        <v>7311656</v>
+        <v>7311662</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2890,7 +2890,7 @@
         <v>132723986</v>
       </c>
       <c r="B24" t="n">
-        <v>99153</v>
+        <v>99154</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2984,45 +2984,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132723951</v>
+        <v>132724024</v>
       </c>
       <c r="B25" t="n">
-        <v>91872</v>
+        <v>99119</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>870232</v>
+        <v>870184</v>
       </c>
       <c r="R25" t="n">
-        <v>7311643</v>
+        <v>7311672</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3063,6 +3071,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3081,10 +3090,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132723942</v>
+        <v>132723980</v>
       </c>
       <c r="B26" t="n">
-        <v>106229</v>
+        <v>57145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,21 +3101,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221725</v>
+        <v>102613</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3116,10 +3125,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>870192</v>
+        <v>870050</v>
       </c>
       <c r="R26" t="n">
-        <v>7311681</v>
+        <v>7311668</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3178,10 +3187,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132723980</v>
+        <v>132723951</v>
       </c>
       <c r="B27" t="n">
-        <v>57144</v>
+        <v>91873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3189,21 +3198,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102613</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3213,10 +3222,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>870050</v>
+        <v>870232</v>
       </c>
       <c r="R27" t="n">
-        <v>7311668</v>
+        <v>7311643</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3275,49 +3284,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132724026</v>
+        <v>132723942</v>
       </c>
       <c r="B28" t="n">
-        <v>99119</v>
+        <v>106230</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>870175</v>
+        <v>870192</v>
       </c>
       <c r="R28" t="n">
-        <v>7311661</v>
+        <v>7311681</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3358,7 +3363,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3377,7 +3381,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132724024</v>
+        <v>132724026</v>
       </c>
       <c r="B29" t="n">
         <v>99119</v>
@@ -3407,23 +3411,19 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870184</v>
+        <v>870175</v>
       </c>
       <c r="R29" t="n">
-        <v>7311672</v>
+        <v>7311661</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3483,45 +3483,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132723948</v>
+        <v>132724015</v>
       </c>
       <c r="B30" t="n">
-        <v>91872</v>
+        <v>99119</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>870106</v>
+        <v>870248</v>
       </c>
       <c r="R30" t="n">
-        <v>7311660</v>
+        <v>7311676</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3562,6 +3566,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3580,10 +3585,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132724015</v>
+        <v>132723958</v>
       </c>
       <c r="B31" t="n">
-        <v>99119</v>
+        <v>92638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3591,38 +3596,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>870248</v>
+        <v>870140</v>
       </c>
       <c r="R31" t="n">
-        <v>7311676</v>
+        <v>7311665</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3663,7 +3664,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3784,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132723958</v>
+        <v>132723948</v>
       </c>
       <c r="B33" t="n">
-        <v>92638</v>
+        <v>91873</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>870140</v>
+        <v>870106</v>
       </c>
       <c r="R33" t="n">
-        <v>7311665</v>
+        <v>7311660</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3881,53 +3881,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132723984</v>
+        <v>132724043</v>
       </c>
       <c r="B34" t="n">
-        <v>99154</v>
+        <v>79328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>870326</v>
+        <v>870268</v>
       </c>
       <c r="R34" t="n">
-        <v>7311673</v>
+        <v>7311645</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3962,18 +3954,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3995,7 +3981,7 @@
         <v>132724042</v>
       </c>
       <c r="B35" t="n">
-        <v>92329</v>
+        <v>92330</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4094,10 +4080,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132723946</v>
+        <v>132723941</v>
       </c>
       <c r="B36" t="n">
-        <v>91872</v>
+        <v>106230</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4105,21 +4091,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4129,10 +4115,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870305</v>
+        <v>870223</v>
       </c>
       <c r="R36" t="n">
-        <v>7311691</v>
+        <v>7311680</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4191,45 +4177,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132724043</v>
+        <v>132723984</v>
       </c>
       <c r="B37" t="n">
-        <v>79327</v>
+        <v>99154</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>870268</v>
+        <v>870326</v>
       </c>
       <c r="R37" t="n">
-        <v>7311645</v>
+        <v>7311673</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4264,12 +4258,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4288,10 +4288,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132723941</v>
+        <v>132723946</v>
       </c>
       <c r="B38" t="n">
-        <v>106229</v>
+        <v>91873</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4299,21 +4299,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>870223</v>
+        <v>870305</v>
       </c>
       <c r="R38" t="n">
-        <v>7311680</v>
+        <v>7311691</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4385,32 +4385,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132723985</v>
+        <v>132724033</v>
       </c>
       <c r="B39" t="n">
-        <v>99153</v>
+        <v>99119</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>870161</v>
+        <v>870089</v>
       </c>
       <c r="R39" t="n">
-        <v>7311671</v>
+        <v>7311673</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4485,7 +4485,7 @@
         <v>132723977</v>
       </c>
       <c r="B40" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4579,10 +4579,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132723940</v>
+        <v>132723957</v>
       </c>
       <c r="B41" t="n">
-        <v>106229</v>
+        <v>80462</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,21 +4590,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>870139</v>
+        <v>870341</v>
       </c>
       <c r="R41" t="n">
-        <v>7311657</v>
+        <v>7311668</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132723943</v>
+        <v>132723940</v>
       </c>
       <c r="B42" t="n">
-        <v>106229</v>
+        <v>106230</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870194</v>
+        <v>870139</v>
       </c>
       <c r="R42" t="n">
-        <v>7311676</v>
+        <v>7311657</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4773,32 +4773,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132724033</v>
+        <v>132723985</v>
       </c>
       <c r="B43" t="n">
-        <v>99118</v>
+        <v>99154</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870089</v>
+        <v>870161</v>
       </c>
       <c r="R43" t="n">
-        <v>7311673</v>
+        <v>7311671</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132723957</v>
+        <v>132723943</v>
       </c>
       <c r="B44" t="n">
-        <v>80461</v>
+        <v>106230</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>870341</v>
+        <v>870194</v>
       </c>
       <c r="R44" t="n">
-        <v>7311668</v>
+        <v>7311676</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4967,45 +4967,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132723963</v>
+        <v>132724020</v>
       </c>
       <c r="B45" t="n">
-        <v>57950</v>
+        <v>99119</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>870057</v>
+        <v>870092</v>
       </c>
       <c r="R45" t="n">
-        <v>7311663</v>
+        <v>7311665</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5046,6 +5050,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5064,49 +5069,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132724020</v>
+        <v>132723963</v>
       </c>
       <c r="B46" t="n">
-        <v>99119</v>
+        <v>57951</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>870092</v>
+        <v>870057</v>
       </c>
       <c r="R46" t="n">
-        <v>7311665</v>
+        <v>7311663</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5147,7 +5148,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5166,45 +5166,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132723964</v>
+        <v>132724010</v>
       </c>
       <c r="B47" t="n">
-        <v>57950</v>
+        <v>99119</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>870194</v>
+        <v>870185</v>
       </c>
       <c r="R47" t="n">
-        <v>7311653</v>
+        <v>7311680</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5245,6 +5249,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5263,49 +5268,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132724010</v>
+        <v>132723964</v>
       </c>
       <c r="B48" t="n">
-        <v>99119</v>
+        <v>57951</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>870185</v>
+        <v>870194</v>
       </c>
       <c r="R48" t="n">
-        <v>7311680</v>
+        <v>7311653</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5346,7 +5347,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5471,49 +5471,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132724019</v>
+        <v>132723983</v>
       </c>
       <c r="B50" t="n">
-        <v>99119</v>
+        <v>99154</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>870221</v>
+        <v>870255</v>
       </c>
       <c r="R50" t="n">
-        <v>7311678</v>
+        <v>7311639</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5546,6 +5550,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5573,45 +5582,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132723954</v>
+        <v>132724019</v>
       </c>
       <c r="B51" t="n">
-        <v>92633</v>
+        <v>99119</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>870345</v>
+        <v>870221</v>
       </c>
       <c r="R51" t="n">
-        <v>7311658</v>
+        <v>7311678</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5652,6 +5665,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5670,10 +5684,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132723983</v>
+        <v>132723954</v>
       </c>
       <c r="B52" t="n">
-        <v>99154</v>
+        <v>92633</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5681,42 +5695,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219874</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>870255</v>
+        <v>870345</v>
       </c>
       <c r="R52" t="n">
-        <v>7311639</v>
+        <v>7311658</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5751,18 +5757,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5781,7 +5781,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132724027</v>
+        <v>132724011</v>
       </c>
       <c r="B53" t="n">
         <v>99119</v>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>870230</v>
+        <v>870148</v>
       </c>
       <c r="R53" t="n">
-        <v>7311672</v>
+        <v>7311649</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132724021</v>
+        <v>132724027</v>
       </c>
       <c r="B54" t="n">
         <v>99119</v>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>870163</v>
+        <v>870230</v>
       </c>
       <c r="R54" t="n">
-        <v>7311664</v>
+        <v>7311672</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6087,7 +6087,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132724011</v>
+        <v>132724021</v>
       </c>
       <c r="B56" t="n">
         <v>99119</v>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>870148</v>
+        <v>870163</v>
       </c>
       <c r="R56" t="n">
-        <v>7311649</v>
+        <v>7311664</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6189,32 +6189,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132723939</v>
+        <v>132723952</v>
       </c>
       <c r="B57" t="n">
-        <v>106229</v>
+        <v>91910</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>870106</v>
+        <v>870242</v>
       </c>
       <c r="R57" t="n">
-        <v>7311664</v>
+        <v>7311674</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6286,32 +6286,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132723952</v>
+        <v>132723939</v>
       </c>
       <c r="B58" t="n">
-        <v>91909</v>
+        <v>106230</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6321,10 +6321,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>870242</v>
+        <v>870106</v>
       </c>
       <c r="R58" t="n">
-        <v>7311674</v>
+        <v>7311664</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6485,10 +6485,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132724028</v>
+        <v>132724017</v>
       </c>
       <c r="B60" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6513,17 +6513,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>870101</v>
+        <v>870091</v>
       </c>
       <c r="R60" t="n">
-        <v>7311647</v>
+        <v>7311660</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6556,11 +6560,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>5 dm2</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6588,7 +6587,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132724017</v>
+        <v>132724028</v>
       </c>
       <c r="B61" t="n">
         <v>99119</v>
@@ -6616,21 +6615,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>870091</v>
+        <v>870101</v>
       </c>
       <c r="R61" t="n">
-        <v>7311660</v>
+        <v>7311647</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6665,6 +6660,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>5 dm2</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6687,6 +6687,104 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132724047</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>870262</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7311642</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132724032</v>
+        <v>132723966</v>
       </c>
       <c r="B3" t="n">
-        <v>99119</v>
+        <v>57951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870091</v>
+        <v>870207</v>
       </c>
       <c r="R3" t="n">
-        <v>7311673</v>
+        <v>7311650</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
         <v>132723979</v>
       </c>
       <c r="B4" t="n">
-        <v>97990</v>
+        <v>97992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132723966</v>
+        <v>132724032</v>
       </c>
       <c r="B5" t="n">
-        <v>57951</v>
+        <v>99121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>870207</v>
+        <v>870091</v>
       </c>
       <c r="R5" t="n">
-        <v>7311650</v>
+        <v>7311673</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132724035</v>
+        <v>132723950</v>
       </c>
       <c r="B6" t="n">
-        <v>57133</v>
+        <v>91875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>870226</v>
+        <v>870220</v>
       </c>
       <c r="R6" t="n">
-        <v>7311649</v>
+        <v>7311651</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132723950</v>
+        <v>132724035</v>
       </c>
       <c r="B7" t="n">
-        <v>91873</v>
+        <v>57133</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870220</v>
+        <v>870226</v>
       </c>
       <c r="R7" t="n">
-        <v>7311651</v>
+        <v>7311649</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132724008</v>
+        <v>132723960</v>
       </c>
       <c r="B8" t="n">
-        <v>99119</v>
+        <v>92640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,38 +1283,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>870160</v>
+        <v>870208</v>
       </c>
       <c r="R8" t="n">
-        <v>7311638</v>
+        <v>7311661</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1355,7 +1351,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1374,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132723960</v>
+        <v>132724008</v>
       </c>
       <c r="B9" t="n">
-        <v>92638</v>
+        <v>99121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,34 +1380,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>870208</v>
+        <v>870160</v>
       </c>
       <c r="R9" t="n">
-        <v>7311661</v>
+        <v>7311638</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1453,6 +1452,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1589,46 +1589,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132724009</v>
+        <v>132723968</v>
       </c>
       <c r="B11" t="n">
-        <v>99119</v>
+        <v>57951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>870145</v>
+        <v>870266</v>
       </c>
       <c r="R11" t="n">
         <v>7311659</v>
@@ -1672,7 +1668,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1691,42 +1686,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132723968</v>
+        <v>132724009</v>
       </c>
       <c r="B12" t="n">
-        <v>57951</v>
+        <v>99121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>870266</v>
+        <v>870145</v>
       </c>
       <c r="R12" t="n">
         <v>7311659</v>
@@ -1770,6 +1769,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>132724013</v>
       </c>
       <c r="B13" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,32 +1890,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132723938</v>
+        <v>132723962</v>
       </c>
       <c r="B14" t="n">
-        <v>106230</v>
+        <v>57951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>870177</v>
+        <v>870045</v>
       </c>
       <c r="R14" t="n">
-        <v>7311649</v>
+        <v>7311671</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1990,7 +1990,7 @@
         <v>132724030</v>
       </c>
       <c r="B15" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2089,32 +2089,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132723962</v>
+        <v>132723938</v>
       </c>
       <c r="B16" t="n">
-        <v>57951</v>
+        <v>106232</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>870045</v>
+        <v>870177</v>
       </c>
       <c r="R16" t="n">
-        <v>7311671</v>
+        <v>7311649</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132723947</v>
+        <v>132723949</v>
       </c>
       <c r="B17" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>870140</v>
+        <v>870194</v>
       </c>
       <c r="R17" t="n">
-        <v>7311665</v>
+        <v>7311657</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2283,10 +2283,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132723949</v>
+        <v>132723947</v>
       </c>
       <c r="B18" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>870194</v>
+        <v>870140</v>
       </c>
       <c r="R18" t="n">
-        <v>7311657</v>
+        <v>7311665</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2383,7 +2383,7 @@
         <v>132724029</v>
       </c>
       <c r="B19" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,32 +2483,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132724046</v>
+        <v>132723969</v>
       </c>
       <c r="B20" t="n">
-        <v>93234</v>
+        <v>57951</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>870273</v>
+        <v>870248</v>
       </c>
       <c r="R20" t="n">
-        <v>7311688</v>
+        <v>7311673</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2556,18 +2556,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp men enbart gran runt om.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2586,32 +2580,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132723969</v>
+        <v>132724046</v>
       </c>
       <c r="B21" t="n">
-        <v>57951</v>
+        <v>93236</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2621,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>870248</v>
+        <v>870273</v>
       </c>
       <c r="R21" t="n">
-        <v>7311673</v>
+        <v>7311688</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2659,12 +2653,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp men enbart gran runt om.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>132724012</v>
       </c>
       <c r="B22" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>132724031</v>
       </c>
       <c r="B23" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>132723986</v>
       </c>
       <c r="B24" t="n">
-        <v>99154</v>
+        <v>99156</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2984,53 +2984,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132724024</v>
+        <v>132723980</v>
       </c>
       <c r="B25" t="n">
-        <v>99119</v>
+        <v>57145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>870184</v>
+        <v>870050</v>
       </c>
       <c r="R25" t="n">
-        <v>7311672</v>
+        <v>7311668</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3071,7 +3063,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3090,45 +3081,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132723980</v>
+        <v>132724024</v>
       </c>
       <c r="B26" t="n">
-        <v>57145</v>
+        <v>99121</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>870050</v>
+        <v>870184</v>
       </c>
       <c r="R26" t="n">
-        <v>7311668</v>
+        <v>7311672</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3169,6 +3168,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3187,45 +3187,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132723951</v>
+        <v>132724026</v>
       </c>
       <c r="B27" t="n">
-        <v>91873</v>
+        <v>99121</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>870232</v>
+        <v>870175</v>
       </c>
       <c r="R27" t="n">
-        <v>7311643</v>
+        <v>7311661</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3266,6 +3270,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3287,7 +3292,7 @@
         <v>132723942</v>
       </c>
       <c r="B28" t="n">
-        <v>106230</v>
+        <v>106232</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3381,49 +3386,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132724026</v>
+        <v>132723951</v>
       </c>
       <c r="B29" t="n">
-        <v>99119</v>
+        <v>91875</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870175</v>
+        <v>870232</v>
       </c>
       <c r="R29" t="n">
-        <v>7311661</v>
+        <v>7311643</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3464,7 +3465,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>132724015</v>
       </c>
       <c r="B30" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3585,10 +3585,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132723958</v>
+        <v>132724023</v>
       </c>
       <c r="B31" t="n">
-        <v>92638</v>
+        <v>99121</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3596,34 +3596,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>870140</v>
+        <v>870206</v>
       </c>
       <c r="R31" t="n">
-        <v>7311665</v>
+        <v>7311679</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3664,6 +3668,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3682,49 +3687,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132724023</v>
+        <v>132723948</v>
       </c>
       <c r="B32" t="n">
-        <v>99119</v>
+        <v>91875</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>870206</v>
+        <v>870106</v>
       </c>
       <c r="R32" t="n">
-        <v>7311679</v>
+        <v>7311660</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3765,7 +3766,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3784,32 +3784,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132723948</v>
+        <v>132723958</v>
       </c>
       <c r="B33" t="n">
-        <v>91873</v>
+        <v>92640</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>870106</v>
+        <v>870140</v>
       </c>
       <c r="R33" t="n">
-        <v>7311660</v>
+        <v>7311665</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3881,32 +3881,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132724043</v>
+        <v>132723946</v>
       </c>
       <c r="B34" t="n">
-        <v>79328</v>
+        <v>91875</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>870268</v>
+        <v>870305</v>
       </c>
       <c r="R34" t="n">
-        <v>7311645</v>
+        <v>7311691</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132724042</v>
+        <v>132724043</v>
       </c>
       <c r="B35" t="n">
-        <v>92330</v>
+        <v>79328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3989,38 +3989,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>870261</v>
+        <v>870268</v>
       </c>
       <c r="R35" t="n">
-        <v>7311655</v>
+        <v>7311645</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4061,7 +4057,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4080,10 +4075,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132723941</v>
+        <v>132723984</v>
       </c>
       <c r="B36" t="n">
-        <v>106230</v>
+        <v>99156</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4091,34 +4086,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870223</v>
+        <v>870326</v>
       </c>
       <c r="R36" t="n">
-        <v>7311680</v>
+        <v>7311673</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4153,12 +4156,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4177,10 +4186,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132723984</v>
+        <v>132723941</v>
       </c>
       <c r="B37" t="n">
-        <v>99154</v>
+        <v>106232</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4188,42 +4197,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>221725</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>870326</v>
+        <v>870223</v>
       </c>
       <c r="R37" t="n">
-        <v>7311673</v>
+        <v>7311680</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4258,18 +4259,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4288,45 +4283,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132723946</v>
+        <v>132724042</v>
       </c>
       <c r="B38" t="n">
-        <v>91873</v>
+        <v>92332</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6040186</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>870305</v>
+        <v>870261</v>
       </c>
       <c r="R38" t="n">
-        <v>7311691</v>
+        <v>7311655</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4367,6 +4366,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4385,32 +4385,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132724033</v>
+        <v>132723957</v>
       </c>
       <c r="B39" t="n">
-        <v>99119</v>
+        <v>80462</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>870089</v>
+        <v>870341</v>
       </c>
       <c r="R39" t="n">
-        <v>7311673</v>
+        <v>7311668</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4485,7 +4485,7 @@
         <v>132723977</v>
       </c>
       <c r="B40" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4579,10 +4579,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132723957</v>
+        <v>132723940</v>
       </c>
       <c r="B41" t="n">
-        <v>80462</v>
+        <v>106232</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,21 +4590,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>870341</v>
+        <v>870139</v>
       </c>
       <c r="R41" t="n">
-        <v>7311668</v>
+        <v>7311657</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132723940</v>
+        <v>132723943</v>
       </c>
       <c r="B42" t="n">
-        <v>106230</v>
+        <v>106232</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870139</v>
+        <v>870194</v>
       </c>
       <c r="R42" t="n">
-        <v>7311657</v>
+        <v>7311676</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4776,7 +4776,7 @@
         <v>132723985</v>
       </c>
       <c r="B43" t="n">
-        <v>99154</v>
+        <v>99156</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,32 +4870,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132723943</v>
+        <v>132724033</v>
       </c>
       <c r="B44" t="n">
-        <v>106230</v>
+        <v>99121</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>870194</v>
+        <v>870089</v>
       </c>
       <c r="R44" t="n">
-        <v>7311676</v>
+        <v>7311673</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4967,49 +4967,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132724020</v>
+        <v>132723963</v>
       </c>
       <c r="B45" t="n">
-        <v>99119</v>
+        <v>57951</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>870092</v>
+        <v>870057</v>
       </c>
       <c r="R45" t="n">
-        <v>7311665</v>
+        <v>7311663</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5050,7 +5046,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5069,45 +5064,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132723963</v>
+        <v>132724020</v>
       </c>
       <c r="B46" t="n">
-        <v>57951</v>
+        <v>99121</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>870057</v>
+        <v>870092</v>
       </c>
       <c r="R46" t="n">
-        <v>7311663</v>
+        <v>7311665</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5148,6 +5147,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132724010</v>
+        <v>132723959</v>
       </c>
       <c r="B47" t="n">
-        <v>99119</v>
+        <v>92640</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5177,38 +5177,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>870185</v>
+        <v>870212</v>
       </c>
       <c r="R47" t="n">
-        <v>7311680</v>
+        <v>7311654</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5241,6 +5240,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gren på granlåga.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5365,10 +5369,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132723959</v>
+        <v>132724010</v>
       </c>
       <c r="B49" t="n">
-        <v>92638</v>
+        <v>99121</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5376,37 +5380,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>870212</v>
+        <v>870185</v>
       </c>
       <c r="R49" t="n">
-        <v>7311654</v>
+        <v>7311680</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5439,11 +5444,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gren på granlåga.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5474,7 +5474,7 @@
         <v>132723983</v>
       </c>
       <c r="B50" t="n">
-        <v>99154</v>
+        <v>99156</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>132724019</v>
       </c>
       <c r="B51" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>132723954</v>
       </c>
       <c r="B52" t="n">
-        <v>92633</v>
+        <v>92635</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>132724011</v>
       </c>
       <c r="B53" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>132724027</v>
       </c>
       <c r="B54" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>132724022</v>
       </c>
       <c r="B55" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>132724021</v>
       </c>
       <c r="B56" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6189,45 +6189,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132723952</v>
+        <v>132724016</v>
       </c>
       <c r="B57" t="n">
-        <v>91910</v>
+        <v>99121</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>870242</v>
+        <v>870243</v>
       </c>
       <c r="R57" t="n">
-        <v>7311674</v>
+        <v>7311678</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6268,6 +6272,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6289,7 +6294,7 @@
         <v>132723939</v>
       </c>
       <c r="B58" t="n">
-        <v>106230</v>
+        <v>106232</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6383,49 +6388,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132724016</v>
+        <v>132723952</v>
       </c>
       <c r="B59" t="n">
-        <v>99119</v>
+        <v>91912</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>870243</v>
+        <v>870242</v>
       </c>
       <c r="R59" t="n">
-        <v>7311678</v>
+        <v>7311674</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6466,7 +6467,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6485,10 +6485,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132724017</v>
+        <v>132724028</v>
       </c>
       <c r="B60" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6513,21 +6513,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>870091</v>
+        <v>870101</v>
       </c>
       <c r="R60" t="n">
-        <v>7311660</v>
+        <v>7311647</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6560,6 +6556,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>5 dm2</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6587,10 +6588,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132724028</v>
+        <v>132724017</v>
       </c>
       <c r="B61" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6615,17 +6616,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>870101</v>
+        <v>870091</v>
       </c>
       <c r="R61" t="n">
-        <v>7311647</v>
+        <v>7311660</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6658,11 +6663,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>5 dm2</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132723966</v>
+        <v>132724032</v>
       </c>
       <c r="B3" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870207</v>
+        <v>870091</v>
       </c>
       <c r="R3" t="n">
-        <v>7311650</v>
+        <v>7311673</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132723979</v>
+        <v>132723966</v>
       </c>
       <c r="B4" t="n">
-        <v>97992</v>
+        <v>57951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870312</v>
+        <v>870207</v>
       </c>
       <c r="R4" t="n">
-        <v>7311654</v>
+        <v>7311650</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132724032</v>
+        <v>132723979</v>
       </c>
       <c r="B5" t="n">
-        <v>99121</v>
+        <v>97993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>870091</v>
+        <v>870312</v>
       </c>
       <c r="R5" t="n">
-        <v>7311673</v>
+        <v>7311654</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132723950</v>
+        <v>132723960</v>
       </c>
       <c r="B6" t="n">
-        <v>91875</v>
+        <v>92641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>870220</v>
+        <v>870208</v>
       </c>
       <c r="R6" t="n">
-        <v>7311651</v>
+        <v>7311661</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1272,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132723960</v>
+        <v>132723950</v>
       </c>
       <c r="B8" t="n">
-        <v>92640</v>
+        <v>91876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>870208</v>
+        <v>870220</v>
       </c>
       <c r="R8" t="n">
-        <v>7311661</v>
+        <v>7311651</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1372,7 +1372,7 @@
         <v>132724008</v>
       </c>
       <c r="B9" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,45 +1471,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132724048</v>
+        <v>132724009</v>
       </c>
       <c r="B10" t="n">
-        <v>78731</v>
+        <v>99122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>870221</v>
+        <v>870145</v>
       </c>
       <c r="R10" t="n">
-        <v>7311646</v>
+        <v>7311659</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1544,11 +1548,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1558,21 +1557,6 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1589,45 +1573,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132723968</v>
+        <v>132724013</v>
       </c>
       <c r="B11" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>870266</v>
+        <v>870190</v>
       </c>
       <c r="R11" t="n">
-        <v>7311659</v>
+        <v>7311676</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1668,6 +1656,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1686,49 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132724009</v>
+        <v>132724048</v>
       </c>
       <c r="B12" t="n">
-        <v>99121</v>
+        <v>78732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>870145</v>
+        <v>870221</v>
       </c>
       <c r="R12" t="n">
-        <v>7311659</v>
+        <v>7311646</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1763,6 +1748,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1772,6 +1762,21 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1788,49 +1793,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132724013</v>
+        <v>132723968</v>
       </c>
       <c r="B13" t="n">
-        <v>99121</v>
+        <v>57951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>870190</v>
+        <v>870266</v>
       </c>
       <c r="R13" t="n">
-        <v>7311676</v>
+        <v>7311659</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1871,7 +1872,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1987,49 +1987,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132724030</v>
+        <v>132723938</v>
       </c>
       <c r="B15" t="n">
-        <v>99121</v>
+        <v>106233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>870251</v>
+        <v>870177</v>
       </c>
       <c r="R15" t="n">
-        <v>7311687</v>
+        <v>7311649</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2070,7 +2066,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2089,45 +2084,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132723938</v>
+        <v>132724030</v>
       </c>
       <c r="B16" t="n">
-        <v>106232</v>
+        <v>99122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>870177</v>
+        <v>870251</v>
       </c>
       <c r="R16" t="n">
-        <v>7311649</v>
+        <v>7311687</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2168,6 +2167,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132723949</v>
+        <v>132723947</v>
       </c>
       <c r="B17" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>870194</v>
+        <v>870140</v>
       </c>
       <c r="R17" t="n">
-        <v>7311657</v>
+        <v>7311665</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2283,10 +2283,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132723947</v>
+        <v>132723949</v>
       </c>
       <c r="B18" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>870140</v>
+        <v>870194</v>
       </c>
       <c r="R18" t="n">
-        <v>7311665</v>
+        <v>7311657</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2383,7 +2383,7 @@
         <v>132724029</v>
       </c>
       <c r="B19" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,32 +2483,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132723969</v>
+        <v>132724046</v>
       </c>
       <c r="B20" t="n">
-        <v>57951</v>
+        <v>93237</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>870248</v>
+        <v>870273</v>
       </c>
       <c r="R20" t="n">
-        <v>7311673</v>
+        <v>7311688</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2556,12 +2556,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp men enbart gran runt om.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2580,32 +2586,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132724046</v>
+        <v>132723969</v>
       </c>
       <c r="B21" t="n">
-        <v>93236</v>
+        <v>57951</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2615,10 +2621,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>870273</v>
+        <v>870248</v>
       </c>
       <c r="R21" t="n">
-        <v>7311688</v>
+        <v>7311673</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2653,18 +2659,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp men enbart gran runt om.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>132724012</v>
       </c>
       <c r="B22" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>132724031</v>
       </c>
       <c r="B23" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>132723986</v>
       </c>
       <c r="B24" t="n">
-        <v>99156</v>
+        <v>99157</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132723980</v>
+        <v>132723951</v>
       </c>
       <c r="B25" t="n">
-        <v>57145</v>
+        <v>91876</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2995,21 +2995,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102613</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>870050</v>
+        <v>870232</v>
       </c>
       <c r="R25" t="n">
-        <v>7311668</v>
+        <v>7311643</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3084,7 +3084,7 @@
         <v>132724024</v>
       </c>
       <c r="B26" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>132724026</v>
       </c>
       <c r="B27" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3289,10 +3289,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132723942</v>
+        <v>132723980</v>
       </c>
       <c r="B28" t="n">
-        <v>106232</v>
+        <v>57145</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3300,21 +3300,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>102613</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>870192</v>
+        <v>870050</v>
       </c>
       <c r="R28" t="n">
-        <v>7311681</v>
+        <v>7311668</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132723951</v>
+        <v>132723942</v>
       </c>
       <c r="B29" t="n">
-        <v>91875</v>
+        <v>106233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870232</v>
+        <v>870192</v>
       </c>
       <c r="R29" t="n">
-        <v>7311643</v>
+        <v>7311681</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3483,10 +3483,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132724015</v>
+        <v>132723958</v>
       </c>
       <c r="B30" t="n">
-        <v>99121</v>
+        <v>92641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3494,38 +3494,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>870248</v>
+        <v>870140</v>
       </c>
       <c r="R30" t="n">
-        <v>7311676</v>
+        <v>7311665</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3566,7 +3562,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3585,49 +3580,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132724023</v>
+        <v>132723948</v>
       </c>
       <c r="B31" t="n">
-        <v>99121</v>
+        <v>91876</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>870206</v>
+        <v>870106</v>
       </c>
       <c r="R31" t="n">
-        <v>7311679</v>
+        <v>7311660</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3668,7 +3659,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3687,45 +3677,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132723948</v>
+        <v>132724015</v>
       </c>
       <c r="B32" t="n">
-        <v>91875</v>
+        <v>99122</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>870106</v>
+        <v>870248</v>
       </c>
       <c r="R32" t="n">
-        <v>7311660</v>
+        <v>7311676</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3766,6 +3760,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3784,10 +3779,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132723958</v>
+        <v>132724023</v>
       </c>
       <c r="B33" t="n">
-        <v>92640</v>
+        <v>99122</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3795,34 +3790,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>870140</v>
+        <v>870206</v>
       </c>
       <c r="R33" t="n">
-        <v>7311665</v>
+        <v>7311679</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3863,6 +3862,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>132723946</v>
       </c>
       <c r="B34" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>132724043</v>
       </c>
       <c r="B35" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4075,53 +4075,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132723984</v>
+        <v>132724042</v>
       </c>
       <c r="B36" t="n">
-        <v>99156</v>
+        <v>92333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219874</v>
+        <v>6040186</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870326</v>
+        <v>870261</v>
       </c>
       <c r="R36" t="n">
-        <v>7311673</v>
+        <v>7311655</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4154,11 +4150,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4186,10 +4177,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132723941</v>
+        <v>132723984</v>
       </c>
       <c r="B37" t="n">
-        <v>106232</v>
+        <v>99157</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4197,34 +4188,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>870223</v>
+        <v>870326</v>
       </c>
       <c r="R37" t="n">
-        <v>7311680</v>
+        <v>7311673</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4259,12 +4258,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4283,49 +4288,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132724042</v>
+        <v>132723941</v>
       </c>
       <c r="B38" t="n">
-        <v>92332</v>
+        <v>106233</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>221725</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>870261</v>
+        <v>870223</v>
       </c>
       <c r="R38" t="n">
-        <v>7311655</v>
+        <v>7311680</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4366,7 +4367,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>132723957</v>
       </c>
       <c r="B39" t="n">
-        <v>80462</v>
+        <v>80463</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132723977</v>
+        <v>132723940</v>
       </c>
       <c r="B40" t="n">
-        <v>97986</v>
+        <v>106233</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>870291</v>
+        <v>870139</v>
       </c>
       <c r="R40" t="n">
-        <v>7311643</v>
+        <v>7311657</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4579,10 +4579,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132723940</v>
+        <v>132723943</v>
       </c>
       <c r="B41" t="n">
-        <v>106232</v>
+        <v>106233</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>870139</v>
+        <v>870194</v>
       </c>
       <c r="R41" t="n">
-        <v>7311657</v>
+        <v>7311676</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132723943</v>
+        <v>132723977</v>
       </c>
       <c r="B42" t="n">
-        <v>106232</v>
+        <v>97987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870194</v>
+        <v>870291</v>
       </c>
       <c r="R42" t="n">
-        <v>7311676</v>
+        <v>7311643</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4773,32 +4773,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132723985</v>
+        <v>132724033</v>
       </c>
       <c r="B43" t="n">
-        <v>99156</v>
+        <v>99122</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870161</v>
+        <v>870089</v>
       </c>
       <c r="R43" t="n">
-        <v>7311671</v>
+        <v>7311673</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4870,32 +4870,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132724033</v>
+        <v>132723985</v>
       </c>
       <c r="B44" t="n">
-        <v>99121</v>
+        <v>99157</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>870089</v>
+        <v>870161</v>
       </c>
       <c r="R44" t="n">
-        <v>7311673</v>
+        <v>7311671</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5067,7 +5067,7 @@
         <v>132724020</v>
       </c>
       <c r="B46" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132723959</v>
+        <v>132724010</v>
       </c>
       <c r="B47" t="n">
-        <v>92640</v>
+        <v>99122</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5177,37 +5177,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>870212</v>
+        <v>870185</v>
       </c>
       <c r="R47" t="n">
-        <v>7311654</v>
+        <v>7311680</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5240,11 +5241,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gren på granlåga.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5272,45 +5268,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132723964</v>
+        <v>132723959</v>
       </c>
       <c r="B48" t="n">
-        <v>57951</v>
+        <v>92641</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>67</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>870194</v>
+        <v>870212</v>
       </c>
       <c r="R48" t="n">
-        <v>7311653</v>
+        <v>7311654</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5345,12 +5344,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gren på granlåga.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5369,49 +5374,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132724010</v>
+        <v>132723964</v>
       </c>
       <c r="B49" t="n">
-        <v>99121</v>
+        <v>57951</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>870185</v>
+        <v>870194</v>
       </c>
       <c r="R49" t="n">
-        <v>7311680</v>
+        <v>7311653</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5452,7 +5453,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>132723983</v>
       </c>
       <c r="B50" t="n">
-        <v>99156</v>
+        <v>99157</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5582,49 +5582,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132724019</v>
+        <v>132723954</v>
       </c>
       <c r="B51" t="n">
-        <v>99121</v>
+        <v>92636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>870221</v>
+        <v>870345</v>
       </c>
       <c r="R51" t="n">
-        <v>7311678</v>
+        <v>7311658</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5665,7 +5661,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5684,45 +5679,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132723954</v>
+        <v>132724019</v>
       </c>
       <c r="B52" t="n">
-        <v>92635</v>
+        <v>99122</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>870345</v>
+        <v>870221</v>
       </c>
       <c r="R52" t="n">
-        <v>7311658</v>
+        <v>7311678</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5763,6 +5762,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>132724011</v>
       </c>
       <c r="B53" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>132724027</v>
       </c>
       <c r="B54" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>132724022</v>
       </c>
       <c r="B55" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>132724021</v>
       </c>
       <c r="B56" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6189,49 +6189,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132724016</v>
+        <v>132723952</v>
       </c>
       <c r="B57" t="n">
-        <v>99121</v>
+        <v>91913</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>870243</v>
+        <v>870242</v>
       </c>
       <c r="R57" t="n">
-        <v>7311678</v>
+        <v>7311674</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6272,7 +6268,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6291,45 +6286,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132723939</v>
+        <v>132724016</v>
       </c>
       <c r="B58" t="n">
-        <v>106232</v>
+        <v>99122</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>870106</v>
+        <v>870243</v>
       </c>
       <c r="R58" t="n">
-        <v>7311664</v>
+        <v>7311678</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6370,6 +6369,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6388,32 +6388,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132723952</v>
+        <v>132723939</v>
       </c>
       <c r="B59" t="n">
-        <v>91912</v>
+        <v>106233</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>870242</v>
+        <v>870106</v>
       </c>
       <c r="R59" t="n">
-        <v>7311674</v>
+        <v>7311664</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6488,7 +6488,7 @@
         <v>132724028</v>
       </c>
       <c r="B60" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>132724017</v>
       </c>
       <c r="B61" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132724032</v>
+        <v>132723966</v>
       </c>
       <c r="B3" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870091</v>
+        <v>870207</v>
       </c>
       <c r="R3" t="n">
-        <v>7311673</v>
+        <v>7311650</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132723966</v>
+        <v>132723979</v>
       </c>
       <c r="B4" t="n">
-        <v>57951</v>
+        <v>97993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870207</v>
+        <v>870312</v>
       </c>
       <c r="R4" t="n">
-        <v>7311650</v>
+        <v>7311654</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132723979</v>
+        <v>132724032</v>
       </c>
       <c r="B5" t="n">
-        <v>97993</v>
+        <v>99122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>870312</v>
+        <v>870091</v>
       </c>
       <c r="R5" t="n">
-        <v>7311654</v>
+        <v>7311673</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1890,32 +1890,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132723962</v>
+        <v>132723938</v>
       </c>
       <c r="B14" t="n">
-        <v>57951</v>
+        <v>106233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>870045</v>
+        <v>870177</v>
       </c>
       <c r="R14" t="n">
-        <v>7311671</v>
+        <v>7311649</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1987,32 +1987,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132723938</v>
+        <v>132723962</v>
       </c>
       <c r="B15" t="n">
-        <v>106233</v>
+        <v>57951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>870177</v>
+        <v>870045</v>
       </c>
       <c r="R15" t="n">
-        <v>7311649</v>
+        <v>7311671</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -3483,32 +3483,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132723958</v>
+        <v>132723948</v>
       </c>
       <c r="B30" t="n">
-        <v>92641</v>
+        <v>91876</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>870140</v>
+        <v>870106</v>
       </c>
       <c r="R30" t="n">
-        <v>7311665</v>
+        <v>7311660</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3580,32 +3580,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132723948</v>
+        <v>132723958</v>
       </c>
       <c r="B31" t="n">
-        <v>91876</v>
+        <v>92641</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>870106</v>
+        <v>870140</v>
       </c>
       <c r="R31" t="n">
-        <v>7311660</v>
+        <v>7311665</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4385,32 +4385,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132723957</v>
+        <v>132724033</v>
       </c>
       <c r="B39" t="n">
-        <v>80463</v>
+        <v>99122</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>870341</v>
+        <v>870089</v>
       </c>
       <c r="R39" t="n">
-        <v>7311668</v>
+        <v>7311673</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132723940</v>
+        <v>132723985</v>
       </c>
       <c r="B40" t="n">
-        <v>106233</v>
+        <v>99157</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>870139</v>
+        <v>870161</v>
       </c>
       <c r="R40" t="n">
-        <v>7311657</v>
+        <v>7311671</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4579,10 +4579,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132723943</v>
+        <v>132723957</v>
       </c>
       <c r="B41" t="n">
-        <v>106233</v>
+        <v>80463</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,21 +4590,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>870194</v>
+        <v>870341</v>
       </c>
       <c r="R41" t="n">
-        <v>7311676</v>
+        <v>7311668</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132723977</v>
+        <v>132723940</v>
       </c>
       <c r="B42" t="n">
-        <v>97987</v>
+        <v>106233</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870291</v>
+        <v>870139</v>
       </c>
       <c r="R42" t="n">
-        <v>7311643</v>
+        <v>7311657</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4773,32 +4773,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132724033</v>
+        <v>132723943</v>
       </c>
       <c r="B43" t="n">
-        <v>99122</v>
+        <v>106233</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870089</v>
+        <v>870194</v>
       </c>
       <c r="R43" t="n">
-        <v>7311673</v>
+        <v>7311676</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132723985</v>
+        <v>132723977</v>
       </c>
       <c r="B44" t="n">
-        <v>99157</v>
+        <v>97987</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>870161</v>
+        <v>870291</v>
       </c>
       <c r="R44" t="n">
-        <v>7311671</v>
+        <v>7311643</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5582,45 +5582,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132723954</v>
+        <v>132724019</v>
       </c>
       <c r="B51" t="n">
-        <v>92636</v>
+        <v>99122</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>870345</v>
+        <v>870221</v>
       </c>
       <c r="R51" t="n">
-        <v>7311658</v>
+        <v>7311678</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5661,6 +5665,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5679,49 +5684,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132724019</v>
+        <v>132723954</v>
       </c>
       <c r="B52" t="n">
-        <v>99122</v>
+        <v>92636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>870221</v>
+        <v>870345</v>
       </c>
       <c r="R52" t="n">
-        <v>7311678</v>
+        <v>7311658</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5762,7 +5763,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6286,49 +6286,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132724016</v>
+        <v>132723939</v>
       </c>
       <c r="B58" t="n">
-        <v>99122</v>
+        <v>106233</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>870243</v>
+        <v>870106</v>
       </c>
       <c r="R58" t="n">
-        <v>7311678</v>
+        <v>7311664</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6369,7 +6365,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6388,45 +6383,49 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132723939</v>
+        <v>132724016</v>
       </c>
       <c r="B59" t="n">
-        <v>106233</v>
+        <v>99122</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>870106</v>
+        <v>870243</v>
       </c>
       <c r="R59" t="n">
-        <v>7311664</v>
+        <v>7311678</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6467,6 +6466,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132723966</v>
+        <v>132723979</v>
       </c>
       <c r="B3" t="n">
-        <v>57951</v>
+        <v>97993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870207</v>
+        <v>870312</v>
       </c>
       <c r="R3" t="n">
-        <v>7311650</v>
+        <v>7311654</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132723979</v>
+        <v>132724032</v>
       </c>
       <c r="B4" t="n">
-        <v>97993</v>
+        <v>99122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870312</v>
+        <v>870091</v>
       </c>
       <c r="R4" t="n">
-        <v>7311654</v>
+        <v>7311673</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132724032</v>
+        <v>132723966</v>
       </c>
       <c r="B5" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>870091</v>
+        <v>870207</v>
       </c>
       <c r="R5" t="n">
-        <v>7311673</v>
+        <v>7311650</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132724035</v>
+        <v>132723950</v>
       </c>
       <c r="B7" t="n">
-        <v>57133</v>
+        <v>91876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870226</v>
+        <v>870220</v>
       </c>
       <c r="R7" t="n">
-        <v>7311649</v>
+        <v>7311651</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1272,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132723950</v>
+        <v>132724035</v>
       </c>
       <c r="B8" t="n">
-        <v>91876</v>
+        <v>57133</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>870220</v>
+        <v>870226</v>
       </c>
       <c r="R8" t="n">
-        <v>7311651</v>
+        <v>7311649</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1471,49 +1471,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132724009</v>
+        <v>132724048</v>
       </c>
       <c r="B10" t="n">
-        <v>99122</v>
+        <v>78732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>870145</v>
+        <v>870221</v>
       </c>
       <c r="R10" t="n">
-        <v>7311659</v>
+        <v>7311646</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,6 +1544,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1557,6 +1558,21 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1573,49 +1589,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132724013</v>
+        <v>132723968</v>
       </c>
       <c r="B11" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>870190</v>
+        <v>870266</v>
       </c>
       <c r="R11" t="n">
-        <v>7311676</v>
+        <v>7311659</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1656,7 +1668,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,45 +1686,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132724048</v>
+        <v>132724009</v>
       </c>
       <c r="B12" t="n">
-        <v>78732</v>
+        <v>99122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>870221</v>
+        <v>870145</v>
       </c>
       <c r="R12" t="n">
-        <v>7311646</v>
+        <v>7311659</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1748,11 +1763,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1762,21 +1772,6 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1793,45 +1788,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132723968</v>
+        <v>132724013</v>
       </c>
       <c r="B13" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>870266</v>
+        <v>870190</v>
       </c>
       <c r="R13" t="n">
-        <v>7311659</v>
+        <v>7311676</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1872,6 +1871,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1987,45 +1987,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132723962</v>
+        <v>132724030</v>
       </c>
       <c r="B15" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>870045</v>
+        <v>870251</v>
       </c>
       <c r="R15" t="n">
-        <v>7311671</v>
+        <v>7311687</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2066,6 +2070,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2084,49 +2089,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132724030</v>
+        <v>132723962</v>
       </c>
       <c r="B16" t="n">
-        <v>99122</v>
+        <v>57951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>870251</v>
+        <v>870045</v>
       </c>
       <c r="R16" t="n">
-        <v>7311687</v>
+        <v>7311671</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2167,7 +2168,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2984,45 +2984,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132723951</v>
+        <v>132724024</v>
       </c>
       <c r="B25" t="n">
-        <v>91876</v>
+        <v>99122</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>870232</v>
+        <v>870184</v>
       </c>
       <c r="R25" t="n">
-        <v>7311643</v>
+        <v>7311672</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3063,6 +3071,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3081,53 +3090,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132724024</v>
+        <v>132723942</v>
       </c>
       <c r="B26" t="n">
-        <v>99122</v>
+        <v>106233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>870184</v>
+        <v>870192</v>
       </c>
       <c r="R26" t="n">
-        <v>7311672</v>
+        <v>7311681</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3168,7 +3169,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3289,10 +3289,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132723980</v>
+        <v>132723951</v>
       </c>
       <c r="B28" t="n">
-        <v>57145</v>
+        <v>91876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3300,21 +3300,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102613</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>870050</v>
+        <v>870232</v>
       </c>
       <c r="R28" t="n">
-        <v>7311668</v>
+        <v>7311643</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132723942</v>
+        <v>132723980</v>
       </c>
       <c r="B29" t="n">
-        <v>106233</v>
+        <v>57145</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221725</v>
+        <v>102613</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870192</v>
+        <v>870050</v>
       </c>
       <c r="R29" t="n">
-        <v>7311681</v>
+        <v>7311668</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3580,10 +3580,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132723958</v>
+        <v>132724015</v>
       </c>
       <c r="B31" t="n">
-        <v>92641</v>
+        <v>99122</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3591,34 +3591,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>870140</v>
+        <v>870248</v>
       </c>
       <c r="R31" t="n">
-        <v>7311665</v>
+        <v>7311676</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3659,6 +3663,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3677,7 +3682,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132724015</v>
+        <v>132724023</v>
       </c>
       <c r="B32" t="n">
         <v>99122</v>
@@ -3707,7 +3712,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3716,10 +3721,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>870248</v>
+        <v>870206</v>
       </c>
       <c r="R32" t="n">
-        <v>7311676</v>
+        <v>7311679</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3779,10 +3784,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132724023</v>
+        <v>132723958</v>
       </c>
       <c r="B33" t="n">
-        <v>99122</v>
+        <v>92641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3790,38 +3795,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>870206</v>
+        <v>870140</v>
       </c>
       <c r="R33" t="n">
-        <v>7311679</v>
+        <v>7311665</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3862,7 +3863,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3881,32 +3881,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132723946</v>
+        <v>132724043</v>
       </c>
       <c r="B34" t="n">
-        <v>91876</v>
+        <v>79329</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>870305</v>
+        <v>870268</v>
       </c>
       <c r="R34" t="n">
-        <v>7311691</v>
+        <v>7311645</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132724043</v>
+        <v>132723946</v>
       </c>
       <c r="B35" t="n">
-        <v>79329</v>
+        <v>91876</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>870268</v>
+        <v>870305</v>
       </c>
       <c r="R35" t="n">
-        <v>7311645</v>
+        <v>7311691</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4075,49 +4075,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132724042</v>
+        <v>132723941</v>
       </c>
       <c r="B36" t="n">
-        <v>92333</v>
+        <v>106233</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6040186</v>
+        <v>221725</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870261</v>
+        <v>870223</v>
       </c>
       <c r="R36" t="n">
-        <v>7311655</v>
+        <v>7311680</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4158,7 +4154,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4288,45 +4283,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132723941</v>
+        <v>132724042</v>
       </c>
       <c r="B38" t="n">
-        <v>106233</v>
+        <v>92333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221725</v>
+        <v>6040186</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>870223</v>
+        <v>870261</v>
       </c>
       <c r="R38" t="n">
-        <v>7311680</v>
+        <v>7311655</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4367,6 +4366,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4385,32 +4385,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132724033</v>
+        <v>132723957</v>
       </c>
       <c r="B39" t="n">
-        <v>99122</v>
+        <v>80463</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>870089</v>
+        <v>870341</v>
       </c>
       <c r="R39" t="n">
-        <v>7311673</v>
+        <v>7311668</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132723985</v>
+        <v>132723977</v>
       </c>
       <c r="B40" t="n">
-        <v>99157</v>
+        <v>97987</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>870161</v>
+        <v>870291</v>
       </c>
       <c r="R40" t="n">
-        <v>7311671</v>
+        <v>7311643</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4579,10 +4579,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132723957</v>
+        <v>132723940</v>
       </c>
       <c r="B41" t="n">
-        <v>80463</v>
+        <v>106233</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,21 +4590,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>870341</v>
+        <v>870139</v>
       </c>
       <c r="R41" t="n">
-        <v>7311668</v>
+        <v>7311657</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4676,32 +4676,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132723940</v>
+        <v>132724033</v>
       </c>
       <c r="B42" t="n">
-        <v>106233</v>
+        <v>99122</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870139</v>
+        <v>870089</v>
       </c>
       <c r="R42" t="n">
-        <v>7311657</v>
+        <v>7311673</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132723977</v>
+        <v>132723985</v>
       </c>
       <c r="B44" t="n">
-        <v>97987</v>
+        <v>99157</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>870291</v>
+        <v>870161</v>
       </c>
       <c r="R44" t="n">
-        <v>7311643</v>
+        <v>7311671</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132724010</v>
+        <v>132723959</v>
       </c>
       <c r="B47" t="n">
-        <v>99122</v>
+        <v>92641</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5177,38 +5177,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>870185</v>
+        <v>870212</v>
       </c>
       <c r="R47" t="n">
-        <v>7311680</v>
+        <v>7311654</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5241,6 +5240,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gren på granlåga.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5268,48 +5272,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132723959</v>
+        <v>132723964</v>
       </c>
       <c r="B48" t="n">
-        <v>92641</v>
+        <v>57951</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>67</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>870212</v>
+        <v>870194</v>
       </c>
       <c r="R48" t="n">
-        <v>7311654</v>
+        <v>7311653</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5344,18 +5345,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gren på granlåga.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5374,45 +5369,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132723964</v>
+        <v>132724010</v>
       </c>
       <c r="B49" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>870194</v>
+        <v>870185</v>
       </c>
       <c r="R49" t="n">
-        <v>7311653</v>
+        <v>7311680</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5453,6 +5452,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5471,10 +5471,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132723983</v>
+        <v>132723954</v>
       </c>
       <c r="B50" t="n">
-        <v>99157</v>
+        <v>92636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5482,42 +5482,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219874</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>870255</v>
+        <v>870345</v>
       </c>
       <c r="R50" t="n">
-        <v>7311639</v>
+        <v>7311658</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5552,18 +5544,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5582,49 +5568,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132724019</v>
+        <v>132723983</v>
       </c>
       <c r="B51" t="n">
-        <v>99122</v>
+        <v>99157</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>870221</v>
+        <v>870255</v>
       </c>
       <c r="R51" t="n">
-        <v>7311678</v>
+        <v>7311639</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5657,6 +5647,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5684,45 +5679,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132723954</v>
+        <v>132724019</v>
       </c>
       <c r="B52" t="n">
-        <v>92636</v>
+        <v>99122</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>870345</v>
+        <v>870221</v>
       </c>
       <c r="R52" t="n">
-        <v>7311658</v>
+        <v>7311678</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5763,6 +5762,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -3881,32 +3881,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132724043</v>
+        <v>132723946</v>
       </c>
       <c r="B34" t="n">
-        <v>79329</v>
+        <v>91876</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>870268</v>
+        <v>870305</v>
       </c>
       <c r="R34" t="n">
-        <v>7311645</v>
+        <v>7311691</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132723946</v>
+        <v>132724043</v>
       </c>
       <c r="B35" t="n">
-        <v>91876</v>
+        <v>79329</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>870305</v>
+        <v>870268</v>
       </c>
       <c r="R35" t="n">
-        <v>7311691</v>
+        <v>7311645</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132723979</v>
+        <v>132723966</v>
       </c>
       <c r="B3" t="n">
-        <v>97993</v>
+        <v>57951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870312</v>
+        <v>870207</v>
       </c>
       <c r="R3" t="n">
-        <v>7311654</v>
+        <v>7311650</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132724032</v>
+        <v>132723979</v>
       </c>
       <c r="B4" t="n">
-        <v>99122</v>
+        <v>97993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870091</v>
+        <v>870312</v>
       </c>
       <c r="R4" t="n">
-        <v>7311673</v>
+        <v>7311654</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132723966</v>
+        <v>132724032</v>
       </c>
       <c r="B5" t="n">
-        <v>57951</v>
+        <v>99122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>870207</v>
+        <v>870091</v>
       </c>
       <c r="R5" t="n">
-        <v>7311650</v>
+        <v>7311673</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -2984,53 +2984,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132724024</v>
+        <v>132723951</v>
       </c>
       <c r="B25" t="n">
-        <v>99122</v>
+        <v>91876</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>870184</v>
+        <v>870232</v>
       </c>
       <c r="R25" t="n">
-        <v>7311672</v>
+        <v>7311643</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3071,7 +3063,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3090,10 +3081,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132723942</v>
+        <v>132723980</v>
       </c>
       <c r="B26" t="n">
-        <v>106233</v>
+        <v>57145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3101,21 +3092,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221725</v>
+        <v>102613</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3125,10 +3116,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>870192</v>
+        <v>870050</v>
       </c>
       <c r="R26" t="n">
-        <v>7311681</v>
+        <v>7311668</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3187,7 +3178,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132724026</v>
+        <v>132724024</v>
       </c>
       <c r="B27" t="n">
         <v>99122</v>
@@ -3217,19 +3208,23 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>870175</v>
+        <v>870184</v>
       </c>
       <c r="R27" t="n">
-        <v>7311661</v>
+        <v>7311672</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3289,10 +3284,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132723951</v>
+        <v>132723942</v>
       </c>
       <c r="B28" t="n">
-        <v>91876</v>
+        <v>106233</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3300,21 +3295,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3324,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>870232</v>
+        <v>870192</v>
       </c>
       <c r="R28" t="n">
-        <v>7311643</v>
+        <v>7311681</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3386,45 +3381,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132723980</v>
+        <v>132724026</v>
       </c>
       <c r="B29" t="n">
-        <v>57145</v>
+        <v>99122</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870050</v>
+        <v>870175</v>
       </c>
       <c r="R29" t="n">
-        <v>7311668</v>
+        <v>7311661</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3465,6 +3464,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3483,32 +3483,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132723948</v>
+        <v>132723958</v>
       </c>
       <c r="B30" t="n">
-        <v>91876</v>
+        <v>92641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>870106</v>
+        <v>870140</v>
       </c>
       <c r="R30" t="n">
-        <v>7311660</v>
+        <v>7311665</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3580,49 +3580,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132724015</v>
+        <v>132723948</v>
       </c>
       <c r="B31" t="n">
-        <v>99122</v>
+        <v>91876</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>870248</v>
+        <v>870106</v>
       </c>
       <c r="R31" t="n">
-        <v>7311676</v>
+        <v>7311660</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3663,7 +3659,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3682,7 +3677,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132724023</v>
+        <v>132724015</v>
       </c>
       <c r="B32" t="n">
         <v>99122</v>
@@ -3712,7 +3707,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3721,10 +3716,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>870206</v>
+        <v>870248</v>
       </c>
       <c r="R32" t="n">
-        <v>7311679</v>
+        <v>7311676</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3784,10 +3779,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132723958</v>
+        <v>132724023</v>
       </c>
       <c r="B33" t="n">
-        <v>92641</v>
+        <v>99122</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3795,34 +3790,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>870140</v>
+        <v>870206</v>
       </c>
       <c r="R33" t="n">
-        <v>7311665</v>
+        <v>7311679</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3863,6 +3862,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132724043</v>
+        <v>132723941</v>
       </c>
       <c r="B35" t="n">
-        <v>79329</v>
+        <v>106233</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>870268</v>
+        <v>870223</v>
       </c>
       <c r="R35" t="n">
-        <v>7311645</v>
+        <v>7311680</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4075,10 +4075,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132723941</v>
+        <v>132723984</v>
       </c>
       <c r="B36" t="n">
-        <v>106233</v>
+        <v>99157</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4086,34 +4086,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870223</v>
+        <v>870326</v>
       </c>
       <c r="R36" t="n">
-        <v>7311680</v>
+        <v>7311673</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4148,12 +4156,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4172,53 +4186,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132723984</v>
+        <v>132724042</v>
       </c>
       <c r="B37" t="n">
-        <v>99157</v>
+        <v>92333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>6040186</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>870326</v>
+        <v>870261</v>
       </c>
       <c r="R37" t="n">
-        <v>7311673</v>
+        <v>7311655</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4251,11 +4261,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4283,10 +4288,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132724042</v>
+        <v>132724043</v>
       </c>
       <c r="B38" t="n">
-        <v>92333</v>
+        <v>79329</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4294,38 +4299,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>870261</v>
+        <v>870268</v>
       </c>
       <c r="R38" t="n">
-        <v>7311655</v>
+        <v>7311645</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4366,7 +4367,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132723960</v>
+        <v>132723950</v>
       </c>
       <c r="B6" t="n">
-        <v>92646</v>
+        <v>91881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>870208</v>
+        <v>870220</v>
       </c>
       <c r="R6" t="n">
-        <v>7311661</v>
+        <v>7311651</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132723950</v>
+        <v>132724035</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>57136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870220</v>
+        <v>870226</v>
       </c>
       <c r="R7" t="n">
-        <v>7311651</v>
+        <v>7311649</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1374,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132724035</v>
+        <v>132723960</v>
       </c>
       <c r="B9" t="n">
-        <v>57136</v>
+        <v>92646</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>67</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>870226</v>
+        <v>870208</v>
       </c>
       <c r="R9" t="n">
-        <v>7311649</v>
+        <v>7311661</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132723968</v>
+        <v>132724048</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>78736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>870266</v>
+        <v>870221</v>
       </c>
       <c r="R10" t="n">
-        <v>7311659</v>
+        <v>7311646</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1544,14 +1544,35 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1568,10 +1589,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132724048</v>
+        <v>132723968</v>
       </c>
       <c r="B11" t="n">
-        <v>78736</v>
+        <v>57955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1600,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1624,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>870221</v>
+        <v>870266</v>
       </c>
       <c r="R11" t="n">
-        <v>7311646</v>
+        <v>7311659</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1641,35 +1662,14 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2483,32 +2483,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132723969</v>
+        <v>132724046</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>93242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>870248</v>
+        <v>870273</v>
       </c>
       <c r="R20" t="n">
-        <v>7311673</v>
+        <v>7311688</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2556,12 +2556,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp men enbart gran runt om.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2580,32 +2586,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132724046</v>
+        <v>132723969</v>
       </c>
       <c r="B21" t="n">
-        <v>93242</v>
+        <v>57955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2615,10 +2621,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>870273</v>
+        <v>870248</v>
       </c>
       <c r="R21" t="n">
-        <v>7311688</v>
+        <v>7311673</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2653,18 +2659,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp men enbart gran runt om.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132723951</v>
+        <v>132723980</v>
       </c>
       <c r="B25" t="n">
-        <v>91881</v>
+        <v>57148</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2995,21 +2995,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>102613</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>870232</v>
+        <v>870050</v>
       </c>
       <c r="R25" t="n">
-        <v>7311643</v>
+        <v>7311668</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3081,45 +3081,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132723980</v>
+        <v>132724024</v>
       </c>
       <c r="B26" t="n">
-        <v>57148</v>
+        <v>99130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>870050</v>
+        <v>870184</v>
       </c>
       <c r="R26" t="n">
-        <v>7311668</v>
+        <v>7311672</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3160,6 +3168,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3275,7 +3284,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132724024</v>
+        <v>132724026</v>
       </c>
       <c r="B28" t="n">
         <v>99130</v>
@@ -3305,23 +3314,19 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>870184</v>
+        <v>870175</v>
       </c>
       <c r="R28" t="n">
-        <v>7311672</v>
+        <v>7311661</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3381,49 +3386,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132724026</v>
+        <v>132723951</v>
       </c>
       <c r="B29" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870175</v>
+        <v>870232</v>
       </c>
       <c r="R29" t="n">
-        <v>7311661</v>
+        <v>7311643</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3464,7 +3465,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3483,32 +3483,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132723948</v>
+        <v>132723958</v>
       </c>
       <c r="B30" t="n">
-        <v>91881</v>
+        <v>92646</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>870106</v>
+        <v>870140</v>
       </c>
       <c r="R30" t="n">
-        <v>7311660</v>
+        <v>7311665</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3580,32 +3580,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132723958</v>
+        <v>132723948</v>
       </c>
       <c r="B31" t="n">
-        <v>92646</v>
+        <v>91881</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>870140</v>
+        <v>870106</v>
       </c>
       <c r="R31" t="n">
-        <v>7311665</v>
+        <v>7311660</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3881,32 +3881,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132723946</v>
+        <v>132724043</v>
       </c>
       <c r="B34" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>870305</v>
+        <v>870268</v>
       </c>
       <c r="R34" t="n">
-        <v>7311691</v>
+        <v>7311645</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3978,32 +3978,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132724043</v>
+        <v>132723946</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>870268</v>
+        <v>870305</v>
       </c>
       <c r="R35" t="n">
-        <v>7311645</v>
+        <v>7311691</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4075,10 +4075,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132723984</v>
+        <v>132723941</v>
       </c>
       <c r="B36" t="n">
-        <v>99165</v>
+        <v>106243</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4086,42 +4086,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219874</v>
+        <v>221725</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870326</v>
+        <v>870223</v>
       </c>
       <c r="R36" t="n">
-        <v>7311673</v>
+        <v>7311680</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4156,18 +4148,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4186,45 +4172,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132723941</v>
+        <v>132724042</v>
       </c>
       <c r="B37" t="n">
-        <v>106243</v>
+        <v>92338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221725</v>
+        <v>6040186</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>870223</v>
+        <v>870261</v>
       </c>
       <c r="R37" t="n">
-        <v>7311680</v>
+        <v>7311655</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4265,6 +4255,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4283,49 +4274,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132724042</v>
+        <v>132723984</v>
       </c>
       <c r="B38" t="n">
-        <v>92338</v>
+        <v>99165</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>219874</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>870261</v>
+        <v>870326</v>
       </c>
       <c r="R38" t="n">
-        <v>7311655</v>
+        <v>7311673</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4358,6 +4353,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4482,10 +4482,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132723940</v>
+        <v>132723977</v>
       </c>
       <c r="B40" t="n">
-        <v>106243</v>
+        <v>97995</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>870139</v>
+        <v>870291</v>
       </c>
       <c r="R40" t="n">
-        <v>7311657</v>
+        <v>7311643</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4579,7 +4579,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132723943</v>
+        <v>132723940</v>
       </c>
       <c r="B41" t="n">
         <v>106243</v>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>870194</v>
+        <v>870139</v>
       </c>
       <c r="R41" t="n">
-        <v>7311676</v>
+        <v>7311657</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4676,32 +4676,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132723977</v>
+        <v>132724033</v>
       </c>
       <c r="B42" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870291</v>
+        <v>870089</v>
       </c>
       <c r="R42" t="n">
-        <v>7311643</v>
+        <v>7311673</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4773,32 +4773,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132724033</v>
+        <v>132723943</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>106243</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870089</v>
+        <v>870194</v>
       </c>
       <c r="R43" t="n">
-        <v>7311673</v>
+        <v>7311676</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4967,49 +4967,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132724020</v>
+        <v>132723963</v>
       </c>
       <c r="B45" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>870092</v>
+        <v>870057</v>
       </c>
       <c r="R45" t="n">
-        <v>7311665</v>
+        <v>7311663</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5050,7 +5046,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5069,45 +5064,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132723963</v>
+        <v>132724020</v>
       </c>
       <c r="B46" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>870057</v>
+        <v>870092</v>
       </c>
       <c r="R46" t="n">
-        <v>7311663</v>
+        <v>7311665</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5148,6 +5147,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5166,48 +5166,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132723959</v>
+        <v>132723964</v>
       </c>
       <c r="B47" t="n">
-        <v>92646</v>
+        <v>57955</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>67</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>870212</v>
+        <v>870194</v>
       </c>
       <c r="R47" t="n">
-        <v>7311654</v>
+        <v>7311653</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5242,18 +5239,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gren på granlåga.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5272,45 +5263,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132723964</v>
+        <v>132723959</v>
       </c>
       <c r="B48" t="n">
-        <v>57955</v>
+        <v>92646</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>67</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>870194</v>
+        <v>870212</v>
       </c>
       <c r="R48" t="n">
-        <v>7311653</v>
+        <v>7311654</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5345,12 +5339,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gren på granlåga.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5471,45 +5471,49 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132723954</v>
+        <v>132724019</v>
       </c>
       <c r="B50" t="n">
-        <v>92641</v>
+        <v>99130</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>870345</v>
+        <v>870221</v>
       </c>
       <c r="R50" t="n">
-        <v>7311658</v>
+        <v>7311678</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5550,6 +5554,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5679,49 +5684,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132724019</v>
+        <v>132723954</v>
       </c>
       <c r="B52" t="n">
-        <v>99130</v>
+        <v>92641</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>870221</v>
+        <v>870345</v>
       </c>
       <c r="R52" t="n">
-        <v>7311678</v>
+        <v>7311658</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5762,7 +5763,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6189,32 +6189,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132723939</v>
+        <v>132723952</v>
       </c>
       <c r="B57" t="n">
-        <v>106243</v>
+        <v>91918</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>870106</v>
+        <v>870242</v>
       </c>
       <c r="R57" t="n">
-        <v>7311664</v>
+        <v>7311674</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6286,49 +6286,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132724016</v>
+        <v>132723939</v>
       </c>
       <c r="B58" t="n">
-        <v>99130</v>
+        <v>106243</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>870243</v>
+        <v>870106</v>
       </c>
       <c r="R58" t="n">
-        <v>7311678</v>
+        <v>7311664</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6369,7 +6365,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6388,45 +6383,49 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132723952</v>
+        <v>132724016</v>
       </c>
       <c r="B59" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>870242</v>
+        <v>870243</v>
       </c>
       <c r="R59" t="n">
-        <v>7311674</v>
+        <v>7311678</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6467,6 +6466,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132723979</v>
+        <v>132724032</v>
       </c>
       <c r="B4" t="n">
-        <v>98001</v>
+        <v>99130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870312</v>
+        <v>870091</v>
       </c>
       <c r="R4" t="n">
-        <v>7311654</v>
+        <v>7311673</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132724032</v>
+        <v>132723979</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>98001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>870091</v>
+        <v>870312</v>
       </c>
       <c r="R5" t="n">
-        <v>7311673</v>
+        <v>7311654</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132723950</v>
+        <v>132724035</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>57136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>870220</v>
+        <v>870226</v>
       </c>
       <c r="R6" t="n">
-        <v>7311651</v>
+        <v>7311649</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,45 +1175,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132724035</v>
+        <v>132724008</v>
       </c>
       <c r="B7" t="n">
-        <v>57136</v>
+        <v>99130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870226</v>
+        <v>870160</v>
       </c>
       <c r="R7" t="n">
-        <v>7311649</v>
+        <v>7311638</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1254,6 +1258,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1272,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132724008</v>
+        <v>132723960</v>
       </c>
       <c r="B8" t="n">
-        <v>99130</v>
+        <v>92646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,38 +1288,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>870160</v>
+        <v>870208</v>
       </c>
       <c r="R8" t="n">
-        <v>7311638</v>
+        <v>7311661</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1355,7 +1356,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1374,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132723960</v>
+        <v>132723950</v>
       </c>
       <c r="B9" t="n">
-        <v>92646</v>
+        <v>91881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>870208</v>
+        <v>870220</v>
       </c>
       <c r="R9" t="n">
-        <v>7311661</v>
+        <v>7311651</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1890,45 +1890,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132723962</v>
+        <v>132724030</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>870045</v>
+        <v>870251</v>
       </c>
       <c r="R14" t="n">
-        <v>7311671</v>
+        <v>7311687</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1969,6 +1973,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2084,49 +2089,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132724030</v>
+        <v>132723962</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>870251</v>
+        <v>870045</v>
       </c>
       <c r="R16" t="n">
-        <v>7311687</v>
+        <v>7311671</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2167,7 +2168,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2186,32 +2186,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132723947</v>
+        <v>132724029</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>870140</v>
+        <v>870105</v>
       </c>
       <c r="R17" t="n">
-        <v>7311665</v>
+        <v>7311661</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2259,12 +2259,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>5 dm2.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2283,7 +2289,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132723949</v>
+        <v>132723947</v>
       </c>
       <c r="B18" t="n">
         <v>91881</v>
@@ -2318,10 +2324,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>870194</v>
+        <v>870140</v>
       </c>
       <c r="R18" t="n">
-        <v>7311657</v>
+        <v>7311665</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2380,32 +2386,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132724029</v>
+        <v>132723949</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2415,10 +2421,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>870105</v>
+        <v>870194</v>
       </c>
       <c r="R19" t="n">
-        <v>7311661</v>
+        <v>7311657</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2453,18 +2459,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>5 dm2.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2483,32 +2483,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132724046</v>
+        <v>132723969</v>
       </c>
       <c r="B20" t="n">
-        <v>93242</v>
+        <v>57955</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>870273</v>
+        <v>870248</v>
       </c>
       <c r="R20" t="n">
-        <v>7311688</v>
+        <v>7311673</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2556,18 +2556,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp men enbart gran runt om.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2586,32 +2580,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132723969</v>
+        <v>132724046</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>93242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2621,10 +2615,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>870248</v>
+        <v>870273</v>
       </c>
       <c r="R21" t="n">
-        <v>7311673</v>
+        <v>7311688</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2659,12 +2653,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp men enbart gran runt om.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3081,53 +3081,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132724024</v>
+        <v>132723951</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>870184</v>
+        <v>870232</v>
       </c>
       <c r="R26" t="n">
-        <v>7311672</v>
+        <v>7311643</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3168,7 +3160,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3187,45 +3178,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132723942</v>
+        <v>132724024</v>
       </c>
       <c r="B27" t="n">
-        <v>106243</v>
+        <v>99130</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>870192</v>
+        <v>870184</v>
       </c>
       <c r="R27" t="n">
-        <v>7311681</v>
+        <v>7311672</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3266,6 +3265,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132723951</v>
+        <v>132723942</v>
       </c>
       <c r="B29" t="n">
-        <v>91881</v>
+        <v>106243</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870232</v>
+        <v>870192</v>
       </c>
       <c r="R29" t="n">
-        <v>7311643</v>
+        <v>7311681</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132724043</v>
+        <v>132724042</v>
       </c>
       <c r="B34" t="n">
-        <v>79333</v>
+        <v>92338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3892,34 +3892,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>870268</v>
+        <v>870261</v>
       </c>
       <c r="R34" t="n">
-        <v>7311645</v>
+        <v>7311655</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3960,6 +3964,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4075,32 +4080,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132723941</v>
+        <v>132724043</v>
       </c>
       <c r="B36" t="n">
-        <v>106243</v>
+        <v>79333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4110,10 +4115,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870223</v>
+        <v>870268</v>
       </c>
       <c r="R36" t="n">
-        <v>7311680</v>
+        <v>7311645</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4172,49 +4177,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132724042</v>
+        <v>132723941</v>
       </c>
       <c r="B37" t="n">
-        <v>92338</v>
+        <v>106243</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6040186</v>
+        <v>221725</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>870261</v>
+        <v>870223</v>
       </c>
       <c r="R37" t="n">
-        <v>7311655</v>
+        <v>7311680</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4255,7 +4256,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4676,32 +4676,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132724033</v>
+        <v>132723943</v>
       </c>
       <c r="B42" t="n">
-        <v>99130</v>
+        <v>106243</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870089</v>
+        <v>870194</v>
       </c>
       <c r="R42" t="n">
-        <v>7311673</v>
+        <v>7311676</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4773,32 +4773,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132723943</v>
+        <v>132724033</v>
       </c>
       <c r="B43" t="n">
-        <v>106243</v>
+        <v>99130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870194</v>
+        <v>870089</v>
       </c>
       <c r="R43" t="n">
-        <v>7311676</v>
+        <v>7311673</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5166,45 +5166,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132723964</v>
+        <v>132724010</v>
       </c>
       <c r="B47" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>870194</v>
+        <v>870185</v>
       </c>
       <c r="R47" t="n">
-        <v>7311653</v>
+        <v>7311680</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5245,6 +5249,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5369,49 +5374,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132724010</v>
+        <v>132723964</v>
       </c>
       <c r="B49" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>870185</v>
+        <v>870194</v>
       </c>
       <c r="R49" t="n">
-        <v>7311680</v>
+        <v>7311653</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5452,7 +5453,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5471,49 +5471,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132724019</v>
+        <v>132723954</v>
       </c>
       <c r="B50" t="n">
-        <v>99130</v>
+        <v>92641</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>870221</v>
+        <v>870345</v>
       </c>
       <c r="R50" t="n">
-        <v>7311678</v>
+        <v>7311658</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5554,7 +5550,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5573,53 +5568,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132723983</v>
+        <v>132724019</v>
       </c>
       <c r="B51" t="n">
-        <v>99165</v>
+        <v>99130</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>870255</v>
+        <v>870221</v>
       </c>
       <c r="R51" t="n">
-        <v>7311639</v>
+        <v>7311678</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5652,11 +5643,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5684,10 +5670,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132723954</v>
+        <v>132723983</v>
       </c>
       <c r="B52" t="n">
-        <v>92641</v>
+        <v>99165</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5695,34 +5681,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>219874</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>870345</v>
+        <v>870255</v>
       </c>
       <c r="R52" t="n">
-        <v>7311658</v>
+        <v>7311639</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5757,12 +5751,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6286,45 +6286,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132723939</v>
+        <v>132724016</v>
       </c>
       <c r="B58" t="n">
-        <v>106243</v>
+        <v>99130</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>870106</v>
+        <v>870243</v>
       </c>
       <c r="R58" t="n">
-        <v>7311664</v>
+        <v>7311678</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6365,6 +6369,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6383,49 +6388,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132724016</v>
+        <v>132723939</v>
       </c>
       <c r="B59" t="n">
-        <v>99130</v>
+        <v>106243</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>870243</v>
+        <v>870106</v>
       </c>
       <c r="R59" t="n">
-        <v>7311678</v>
+        <v>7311664</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6466,7 +6467,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132723966</v>
+        <v>132723979</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>98001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870207</v>
+        <v>870312</v>
       </c>
       <c r="R3" t="n">
-        <v>7311650</v>
+        <v>7311654</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132723979</v>
+        <v>132723966</v>
       </c>
       <c r="B5" t="n">
-        <v>98001</v>
+        <v>57955</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>870312</v>
+        <v>870207</v>
       </c>
       <c r="R5" t="n">
-        <v>7311654</v>
+        <v>7311650</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132724035</v>
+        <v>132723950</v>
       </c>
       <c r="B6" t="n">
-        <v>57136</v>
+        <v>91881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>870226</v>
+        <v>870220</v>
       </c>
       <c r="R6" t="n">
-        <v>7311649</v>
+        <v>7311651</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132724008</v>
+        <v>132723960</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>92646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,38 +1186,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870160</v>
+        <v>870208</v>
       </c>
       <c r="R7" t="n">
-        <v>7311638</v>
+        <v>7311661</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1258,7 +1254,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1277,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132723960</v>
+        <v>132724035</v>
       </c>
       <c r="B8" t="n">
-        <v>92646</v>
+        <v>57136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>870208</v>
+        <v>870226</v>
       </c>
       <c r="R8" t="n">
-        <v>7311661</v>
+        <v>7311649</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1374,45 +1369,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132723950</v>
+        <v>132724008</v>
       </c>
       <c r="B9" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>870220</v>
+        <v>870160</v>
       </c>
       <c r="R9" t="n">
-        <v>7311651</v>
+        <v>7311638</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1453,6 +1452,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132724048</v>
+        <v>132723968</v>
       </c>
       <c r="B10" t="n">
-        <v>78736</v>
+        <v>57955</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>870221</v>
+        <v>870266</v>
       </c>
       <c r="R10" t="n">
-        <v>7311646</v>
+        <v>7311659</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1544,35 +1544,14 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1589,42 +1568,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132723968</v>
+        <v>132724009</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>870266</v>
+        <v>870145</v>
       </c>
       <c r="R11" t="n">
         <v>7311659</v>
@@ -1668,6 +1651,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1686,7 +1670,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132724009</v>
+        <v>132724013</v>
       </c>
       <c r="B12" t="n">
         <v>99130</v>
@@ -1716,7 +1700,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>49</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1725,10 +1709,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>870145</v>
+        <v>870190</v>
       </c>
       <c r="R12" t="n">
-        <v>7311659</v>
+        <v>7311676</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1788,49 +1772,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132724013</v>
+        <v>132724048</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>78736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>870190</v>
+        <v>870221</v>
       </c>
       <c r="R13" t="n">
-        <v>7311676</v>
+        <v>7311646</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1865,6 +1845,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1874,6 +1859,21 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1890,49 +1890,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132724030</v>
+        <v>132723962</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>870251</v>
+        <v>870045</v>
       </c>
       <c r="R14" t="n">
-        <v>7311687</v>
+        <v>7311671</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1973,7 +1969,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2089,45 +2084,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132723962</v>
+        <v>132724030</v>
       </c>
       <c r="B16" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>870045</v>
+        <v>870251</v>
       </c>
       <c r="R16" t="n">
-        <v>7311671</v>
+        <v>7311687</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2168,6 +2167,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2186,32 +2186,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132724029</v>
+        <v>132723947</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>870105</v>
+        <v>870140</v>
       </c>
       <c r="R17" t="n">
-        <v>7311661</v>
+        <v>7311665</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2259,18 +2259,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>5 dm2.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2289,7 +2283,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132723947</v>
+        <v>132723949</v>
       </c>
       <c r="B18" t="n">
         <v>91881</v>
@@ -2324,10 +2318,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>870140</v>
+        <v>870194</v>
       </c>
       <c r="R18" t="n">
-        <v>7311665</v>
+        <v>7311657</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2386,32 +2380,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132723949</v>
+        <v>132724029</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2421,10 +2415,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>870194</v>
+        <v>870105</v>
       </c>
       <c r="R19" t="n">
-        <v>7311657</v>
+        <v>7311661</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2459,12 +2453,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>5 dm2.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2984,45 +2984,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132723980</v>
+        <v>132724024</v>
       </c>
       <c r="B25" t="n">
-        <v>57148</v>
+        <v>99130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>870050</v>
+        <v>870184</v>
       </c>
       <c r="R25" t="n">
-        <v>7311668</v>
+        <v>7311672</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3063,6 +3071,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3081,10 +3090,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132723951</v>
+        <v>132723942</v>
       </c>
       <c r="B26" t="n">
-        <v>91881</v>
+        <v>106243</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,21 +3101,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3116,10 +3125,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>870232</v>
+        <v>870192</v>
       </c>
       <c r="R26" t="n">
-        <v>7311643</v>
+        <v>7311681</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3178,7 +3187,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132724024</v>
+        <v>132724026</v>
       </c>
       <c r="B27" t="n">
         <v>99130</v>
@@ -3208,23 +3217,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>870184</v>
+        <v>870175</v>
       </c>
       <c r="R27" t="n">
-        <v>7311672</v>
+        <v>7311661</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3284,49 +3289,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132724026</v>
+        <v>132723951</v>
       </c>
       <c r="B28" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>870175</v>
+        <v>870232</v>
       </c>
       <c r="R28" t="n">
-        <v>7311661</v>
+        <v>7311643</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3367,7 +3368,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132723942</v>
+        <v>132723980</v>
       </c>
       <c r="B29" t="n">
-        <v>106243</v>
+        <v>57148</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3397,21 +3397,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221725</v>
+        <v>102613</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870192</v>
+        <v>870050</v>
       </c>
       <c r="R29" t="n">
-        <v>7311681</v>
+        <v>7311668</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132724042</v>
+        <v>132724043</v>
       </c>
       <c r="B34" t="n">
-        <v>92338</v>
+        <v>79333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3892,38 +3892,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>870261</v>
+        <v>870268</v>
       </c>
       <c r="R34" t="n">
-        <v>7311655</v>
+        <v>7311645</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3964,7 +3960,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3983,10 +3978,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132723946</v>
+        <v>132723941</v>
       </c>
       <c r="B35" t="n">
-        <v>91881</v>
+        <v>106243</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3994,21 +3989,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4018,10 +4013,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>870305</v>
+        <v>870223</v>
       </c>
       <c r="R35" t="n">
-        <v>7311691</v>
+        <v>7311680</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4080,32 +4075,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132724043</v>
+        <v>132723946</v>
       </c>
       <c r="B36" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4115,10 +4110,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870268</v>
+        <v>870305</v>
       </c>
       <c r="R36" t="n">
-        <v>7311645</v>
+        <v>7311691</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4177,10 +4172,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132723941</v>
+        <v>132723984</v>
       </c>
       <c r="B37" t="n">
-        <v>106243</v>
+        <v>99165</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4188,34 +4183,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>870223</v>
+        <v>870326</v>
       </c>
       <c r="R37" t="n">
-        <v>7311680</v>
+        <v>7311673</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4250,12 +4253,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4274,53 +4283,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132723984</v>
+        <v>132724042</v>
       </c>
       <c r="B38" t="n">
-        <v>99165</v>
+        <v>92338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219874</v>
+        <v>6040186</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>870326</v>
+        <v>870261</v>
       </c>
       <c r="R38" t="n">
-        <v>7311673</v>
+        <v>7311655</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4353,11 +4358,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4676,32 +4676,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132723943</v>
+        <v>132724033</v>
       </c>
       <c r="B42" t="n">
-        <v>106243</v>
+        <v>99130</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870194</v>
+        <v>870089</v>
       </c>
       <c r="R42" t="n">
-        <v>7311676</v>
+        <v>7311673</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4773,32 +4773,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132724033</v>
+        <v>132723943</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>106243</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870089</v>
+        <v>870194</v>
       </c>
       <c r="R43" t="n">
-        <v>7311673</v>
+        <v>7311676</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4967,45 +4967,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132723963</v>
+        <v>132724020</v>
       </c>
       <c r="B45" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>870057</v>
+        <v>870092</v>
       </c>
       <c r="R45" t="n">
-        <v>7311663</v>
+        <v>7311665</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5046,6 +5050,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5064,49 +5069,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132724020</v>
+        <v>132723963</v>
       </c>
       <c r="B46" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>870092</v>
+        <v>870057</v>
       </c>
       <c r="R46" t="n">
-        <v>7311665</v>
+        <v>7311663</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5147,7 +5148,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132724010</v>
+        <v>132723959</v>
       </c>
       <c r="B47" t="n">
-        <v>99130</v>
+        <v>92646</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5177,38 +5177,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>870185</v>
+        <v>870212</v>
       </c>
       <c r="R47" t="n">
-        <v>7311680</v>
+        <v>7311654</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5241,6 +5240,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gren på granlåga.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5268,10 +5272,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132723959</v>
+        <v>132724010</v>
       </c>
       <c r="B48" t="n">
-        <v>92646</v>
+        <v>99130</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5279,37 +5283,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>870212</v>
+        <v>870185</v>
       </c>
       <c r="R48" t="n">
-        <v>7311654</v>
+        <v>7311680</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5342,11 +5347,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gren på granlåga.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5568,49 +5568,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132724019</v>
+        <v>132723983</v>
       </c>
       <c r="B51" t="n">
-        <v>99130</v>
+        <v>99165</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>870221</v>
+        <v>870255</v>
       </c>
       <c r="R51" t="n">
-        <v>7311678</v>
+        <v>7311639</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5643,6 +5647,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5670,53 +5679,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132723983</v>
+        <v>132724019</v>
       </c>
       <c r="B52" t="n">
-        <v>99165</v>
+        <v>99130</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>870255</v>
+        <v>870221</v>
       </c>
       <c r="R52" t="n">
-        <v>7311639</v>
+        <v>7311678</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5749,11 +5754,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6286,49 +6286,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132724016</v>
+        <v>132723939</v>
       </c>
       <c r="B58" t="n">
-        <v>99130</v>
+        <v>106243</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>870243</v>
+        <v>870106</v>
       </c>
       <c r="R58" t="n">
-        <v>7311678</v>
+        <v>7311664</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6369,7 +6365,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6388,45 +6383,49 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132723939</v>
+        <v>132724016</v>
       </c>
       <c r="B59" t="n">
-        <v>106243</v>
+        <v>99130</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>870106</v>
+        <v>870243</v>
       </c>
       <c r="R59" t="n">
-        <v>7311664</v>
+        <v>7311678</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6467,6 +6466,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132723960</v>
+        <v>132724008</v>
       </c>
       <c r="B7" t="n">
-        <v>92646</v>
+        <v>99130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,34 +1186,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870208</v>
+        <v>870160</v>
       </c>
       <c r="R7" t="n">
-        <v>7311661</v>
+        <v>7311638</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1254,6 +1258,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1272,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132724035</v>
+        <v>132723960</v>
       </c>
       <c r="B8" t="n">
-        <v>57136</v>
+        <v>92646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>67</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>870226</v>
+        <v>870208</v>
       </c>
       <c r="R8" t="n">
-        <v>7311649</v>
+        <v>7311661</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1369,49 +1374,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132724008</v>
+        <v>132724035</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>57136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>870160</v>
+        <v>870226</v>
       </c>
       <c r="R9" t="n">
-        <v>7311638</v>
+        <v>7311649</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1452,7 +1453,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1471,42 +1471,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132723968</v>
+        <v>132724009</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>870266</v>
+        <v>870145</v>
       </c>
       <c r="R10" t="n">
         <v>7311659</v>
@@ -1550,6 +1554,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1568,7 +1573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132724009</v>
+        <v>132724013</v>
       </c>
       <c r="B11" t="n">
         <v>99130</v>
@@ -1598,7 +1603,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>49</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1607,10 +1612,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>870145</v>
+        <v>870190</v>
       </c>
       <c r="R11" t="n">
-        <v>7311659</v>
+        <v>7311676</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1670,49 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132724013</v>
+        <v>132724048</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>78736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>870190</v>
+        <v>870221</v>
       </c>
       <c r="R12" t="n">
-        <v>7311676</v>
+        <v>7311646</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,6 +1748,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1756,6 +1762,21 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1772,10 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132724048</v>
+        <v>132723968</v>
       </c>
       <c r="B13" t="n">
-        <v>78736</v>
+        <v>57955</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,21 +1804,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1828,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>870221</v>
+        <v>870266</v>
       </c>
       <c r="R13" t="n">
-        <v>7311646</v>
+        <v>7311659</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1845,35 +1866,14 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2186,32 +2186,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132723947</v>
+        <v>132724029</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>870140</v>
+        <v>870105</v>
       </c>
       <c r="R17" t="n">
-        <v>7311665</v>
+        <v>7311661</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2259,12 +2259,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>5 dm2.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2380,32 +2386,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132724029</v>
+        <v>132723947</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2415,10 +2421,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>870105</v>
+        <v>870140</v>
       </c>
       <c r="R19" t="n">
-        <v>7311661</v>
+        <v>7311665</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2453,18 +2459,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>5 dm2.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2483,32 +2483,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132723969</v>
+        <v>132724046</v>
       </c>
       <c r="B20" t="n">
-        <v>57955</v>
+        <v>93242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>870248</v>
+        <v>870273</v>
       </c>
       <c r="R20" t="n">
-        <v>7311673</v>
+        <v>7311688</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2556,12 +2556,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp men enbart gran runt om.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2580,32 +2586,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132724046</v>
+        <v>132723969</v>
       </c>
       <c r="B21" t="n">
-        <v>93242</v>
+        <v>57955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2615,10 +2621,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>870273</v>
+        <v>870248</v>
       </c>
       <c r="R21" t="n">
-        <v>7311688</v>
+        <v>7311673</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2653,18 +2659,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp men enbart gran runt om.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2984,53 +2984,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132724024</v>
+        <v>132723951</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>870184</v>
+        <v>870232</v>
       </c>
       <c r="R25" t="n">
-        <v>7311672</v>
+        <v>7311643</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3071,7 +3063,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3090,10 +3081,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132723942</v>
+        <v>132723980</v>
       </c>
       <c r="B26" t="n">
-        <v>106243</v>
+        <v>57148</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3101,21 +3092,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221725</v>
+        <v>102613</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3125,10 +3116,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>870192</v>
+        <v>870050</v>
       </c>
       <c r="R26" t="n">
-        <v>7311681</v>
+        <v>7311668</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3187,7 +3178,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132724026</v>
+        <v>132724024</v>
       </c>
       <c r="B27" t="n">
         <v>99130</v>
@@ -3217,19 +3208,23 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>870175</v>
+        <v>870184</v>
       </c>
       <c r="R27" t="n">
-        <v>7311661</v>
+        <v>7311672</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3289,10 +3284,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132723951</v>
+        <v>132723942</v>
       </c>
       <c r="B28" t="n">
-        <v>91881</v>
+        <v>106243</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3300,21 +3295,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3324,10 +3319,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>870232</v>
+        <v>870192</v>
       </c>
       <c r="R28" t="n">
-        <v>7311643</v>
+        <v>7311681</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3386,45 +3381,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132723980</v>
+        <v>132724026</v>
       </c>
       <c r="B29" t="n">
-        <v>57148</v>
+        <v>99130</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870050</v>
+        <v>870175</v>
       </c>
       <c r="R29" t="n">
-        <v>7311668</v>
+        <v>7311661</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3465,6 +3464,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3483,32 +3483,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132723958</v>
+        <v>132723948</v>
       </c>
       <c r="B30" t="n">
-        <v>92646</v>
+        <v>91881</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>870140</v>
+        <v>870106</v>
       </c>
       <c r="R30" t="n">
-        <v>7311665</v>
+        <v>7311660</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3580,32 +3580,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132723948</v>
+        <v>132723958</v>
       </c>
       <c r="B31" t="n">
-        <v>91881</v>
+        <v>92646</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>870106</v>
+        <v>870140</v>
       </c>
       <c r="R31" t="n">
-        <v>7311660</v>
+        <v>7311665</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3881,32 +3881,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132724043</v>
+        <v>132723941</v>
       </c>
       <c r="B34" t="n">
-        <v>79333</v>
+        <v>106243</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>870268</v>
+        <v>870223</v>
       </c>
       <c r="R34" t="n">
-        <v>7311645</v>
+        <v>7311680</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3978,45 +3978,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132723941</v>
+        <v>132724042</v>
       </c>
       <c r="B35" t="n">
-        <v>106243</v>
+        <v>92338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221725</v>
+        <v>6040186</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>870223</v>
+        <v>870261</v>
       </c>
       <c r="R35" t="n">
-        <v>7311680</v>
+        <v>7311655</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4057,6 +4061,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4075,10 +4080,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132723946</v>
+        <v>132723984</v>
       </c>
       <c r="B36" t="n">
-        <v>91881</v>
+        <v>99165</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4086,34 +4091,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>219874</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870305</v>
+        <v>870326</v>
       </c>
       <c r="R36" t="n">
-        <v>7311691</v>
+        <v>7311673</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4148,12 +4161,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4172,10 +4191,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132723984</v>
+        <v>132723946</v>
       </c>
       <c r="B37" t="n">
-        <v>99165</v>
+        <v>91881</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4183,42 +4202,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>870326</v>
+        <v>870305</v>
       </c>
       <c r="R37" t="n">
-        <v>7311673</v>
+        <v>7311691</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4253,18 +4264,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4283,10 +4288,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132724042</v>
+        <v>132724043</v>
       </c>
       <c r="B38" t="n">
-        <v>92338</v>
+        <v>79333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4294,38 +4299,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>870261</v>
+        <v>870268</v>
       </c>
       <c r="R38" t="n">
-        <v>7311655</v>
+        <v>7311645</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4366,7 +4367,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132723977</v>
+        <v>132723985</v>
       </c>
       <c r="B40" t="n">
-        <v>97995</v>
+        <v>99165</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>870291</v>
+        <v>870161</v>
       </c>
       <c r="R40" t="n">
-        <v>7311643</v>
+        <v>7311671</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4579,10 +4579,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132723940</v>
+        <v>132723977</v>
       </c>
       <c r="B41" t="n">
-        <v>106243</v>
+        <v>97995</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,21 +4590,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>870139</v>
+        <v>870291</v>
       </c>
       <c r="R41" t="n">
-        <v>7311657</v>
+        <v>7311643</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4676,32 +4676,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132724033</v>
+        <v>132723940</v>
       </c>
       <c r="B42" t="n">
-        <v>99130</v>
+        <v>106243</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870089</v>
+        <v>870139</v>
       </c>
       <c r="R42" t="n">
-        <v>7311673</v>
+        <v>7311657</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4773,32 +4773,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132723943</v>
+        <v>132724033</v>
       </c>
       <c r="B43" t="n">
-        <v>106243</v>
+        <v>99130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870194</v>
+        <v>870089</v>
       </c>
       <c r="R43" t="n">
-        <v>7311676</v>
+        <v>7311673</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132723985</v>
+        <v>132723943</v>
       </c>
       <c r="B44" t="n">
-        <v>99165</v>
+        <v>106243</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>221725</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>870161</v>
+        <v>870194</v>
       </c>
       <c r="R44" t="n">
-        <v>7311671</v>
+        <v>7311676</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4967,49 +4967,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132724020</v>
+        <v>132723963</v>
       </c>
       <c r="B45" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>870092</v>
+        <v>870057</v>
       </c>
       <c r="R45" t="n">
-        <v>7311665</v>
+        <v>7311663</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5050,7 +5046,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5069,45 +5064,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132723963</v>
+        <v>132724020</v>
       </c>
       <c r="B46" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>870057</v>
+        <v>870092</v>
       </c>
       <c r="R46" t="n">
-        <v>7311663</v>
+        <v>7311665</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5148,6 +5147,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5272,49 +5272,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132724010</v>
+        <v>132723964</v>
       </c>
       <c r="B48" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>870185</v>
+        <v>870194</v>
       </c>
       <c r="R48" t="n">
-        <v>7311680</v>
+        <v>7311653</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5355,7 +5351,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5374,45 +5369,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132723964</v>
+        <v>132724010</v>
       </c>
       <c r="B49" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>870194</v>
+        <v>870185</v>
       </c>
       <c r="R49" t="n">
-        <v>7311653</v>
+        <v>7311680</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5453,6 +5452,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5568,53 +5568,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132723983</v>
+        <v>132724019</v>
       </c>
       <c r="B51" t="n">
-        <v>99165</v>
+        <v>99130</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>870255</v>
+        <v>870221</v>
       </c>
       <c r="R51" t="n">
-        <v>7311639</v>
+        <v>7311678</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5647,11 +5643,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5679,49 +5670,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132724019</v>
+        <v>132723983</v>
       </c>
       <c r="B52" t="n">
-        <v>99130</v>
+        <v>99165</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>870221</v>
+        <v>870255</v>
       </c>
       <c r="R52" t="n">
-        <v>7311678</v>
+        <v>7311639</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5754,6 +5749,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -4967,45 +4967,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132723963</v>
+        <v>132724020</v>
       </c>
       <c r="B45" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>870057</v>
+        <v>870092</v>
       </c>
       <c r="R45" t="n">
-        <v>7311663</v>
+        <v>7311665</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5046,6 +5050,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5064,49 +5069,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132724020</v>
+        <v>132723963</v>
       </c>
       <c r="B46" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>870092</v>
+        <v>870057</v>
       </c>
       <c r="R46" t="n">
-        <v>7311665</v>
+        <v>7311663</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5147,7 +5148,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132723979</v>
+        <v>132723966</v>
       </c>
       <c r="B3" t="n">
-        <v>98001</v>
+        <v>57955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870312</v>
+        <v>870207</v>
       </c>
       <c r="R3" t="n">
-        <v>7311654</v>
+        <v>7311650</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132723966</v>
+        <v>132723979</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>98001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>870207</v>
+        <v>870312</v>
       </c>
       <c r="R5" t="n">
-        <v>7311650</v>
+        <v>7311654</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1471,49 +1471,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132724009</v>
+        <v>132724048</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>78736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>870145</v>
+        <v>870221</v>
       </c>
       <c r="R10" t="n">
-        <v>7311659</v>
+        <v>7311646</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,6 +1544,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1557,6 +1558,21 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1573,49 +1589,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132724013</v>
+        <v>132723968</v>
       </c>
       <c r="B11" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>870190</v>
+        <v>870266</v>
       </c>
       <c r="R11" t="n">
-        <v>7311676</v>
+        <v>7311659</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1656,7 +1668,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,45 +1686,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132724048</v>
+        <v>132724009</v>
       </c>
       <c r="B12" t="n">
-        <v>78736</v>
+        <v>99130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>870221</v>
+        <v>870145</v>
       </c>
       <c r="R12" t="n">
-        <v>7311646</v>
+        <v>7311659</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1748,11 +1763,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1762,21 +1772,6 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1793,45 +1788,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132723968</v>
+        <v>132724013</v>
       </c>
       <c r="B13" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>870266</v>
+        <v>870190</v>
       </c>
       <c r="R13" t="n">
-        <v>7311659</v>
+        <v>7311676</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1872,6 +1871,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1987,45 +1987,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132723938</v>
+        <v>132724030</v>
       </c>
       <c r="B15" t="n">
-        <v>106243</v>
+        <v>99130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>870177</v>
+        <v>870251</v>
       </c>
       <c r="R15" t="n">
-        <v>7311649</v>
+        <v>7311687</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2066,6 +2070,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2084,49 +2089,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132724030</v>
+        <v>132723938</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>106243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>870251</v>
+        <v>870177</v>
       </c>
       <c r="R16" t="n">
-        <v>7311687</v>
+        <v>7311649</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2167,7 +2168,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2186,32 +2186,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132724029</v>
+        <v>132723947</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>870105</v>
+        <v>870140</v>
       </c>
       <c r="R17" t="n">
-        <v>7311661</v>
+        <v>7311665</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2259,18 +2259,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>5 dm2.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2386,32 +2380,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132723947</v>
+        <v>132724029</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2421,10 +2415,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>870140</v>
+        <v>870105</v>
       </c>
       <c r="R19" t="n">
-        <v>7311665</v>
+        <v>7311661</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2459,12 +2453,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>5 dm2.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2984,45 +2984,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132723951</v>
+        <v>132724026</v>
       </c>
       <c r="B25" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>870232</v>
+        <v>870175</v>
       </c>
       <c r="R25" t="n">
-        <v>7311643</v>
+        <v>7311661</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3063,6 +3067,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3081,10 +3086,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132723980</v>
+        <v>132723942</v>
       </c>
       <c r="B26" t="n">
-        <v>57148</v>
+        <v>106243</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,21 +3097,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102613</v>
+        <v>221725</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3116,10 +3121,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>870050</v>
+        <v>870192</v>
       </c>
       <c r="R26" t="n">
-        <v>7311668</v>
+        <v>7311681</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3284,10 +3289,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132723942</v>
+        <v>132723951</v>
       </c>
       <c r="B28" t="n">
-        <v>106243</v>
+        <v>91881</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3295,21 +3300,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3319,10 +3324,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>870192</v>
+        <v>870232</v>
       </c>
       <c r="R28" t="n">
-        <v>7311681</v>
+        <v>7311643</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3381,49 +3386,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132724026</v>
+        <v>132723980</v>
       </c>
       <c r="B29" t="n">
-        <v>99130</v>
+        <v>57148</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870175</v>
+        <v>870050</v>
       </c>
       <c r="R29" t="n">
-        <v>7311661</v>
+        <v>7311668</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3464,7 +3465,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3483,32 +3483,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132723948</v>
+        <v>132723958</v>
       </c>
       <c r="B30" t="n">
-        <v>91881</v>
+        <v>92646</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>870106</v>
+        <v>870140</v>
       </c>
       <c r="R30" t="n">
-        <v>7311660</v>
+        <v>7311665</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3580,32 +3580,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132723958</v>
+        <v>132723948</v>
       </c>
       <c r="B31" t="n">
-        <v>92646</v>
+        <v>91881</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>870140</v>
+        <v>870106</v>
       </c>
       <c r="R31" t="n">
-        <v>7311665</v>
+        <v>7311660</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132723941</v>
+        <v>132723984</v>
       </c>
       <c r="B34" t="n">
-        <v>106243</v>
+        <v>99165</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3892,34 +3892,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>870223</v>
+        <v>870326</v>
       </c>
       <c r="R34" t="n">
-        <v>7311680</v>
+        <v>7311673</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3954,12 +3962,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3978,49 +3992,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132724042</v>
+        <v>132723941</v>
       </c>
       <c r="B35" t="n">
-        <v>92338</v>
+        <v>106243</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6040186</v>
+        <v>221725</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>870261</v>
+        <v>870223</v>
       </c>
       <c r="R35" t="n">
-        <v>7311655</v>
+        <v>7311680</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4061,7 +4071,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4080,53 +4089,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132723984</v>
+        <v>132724042</v>
       </c>
       <c r="B36" t="n">
-        <v>99165</v>
+        <v>92338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219874</v>
+        <v>6040186</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870326</v>
+        <v>870261</v>
       </c>
       <c r="R36" t="n">
-        <v>7311673</v>
+        <v>7311655</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4159,11 +4164,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4191,32 +4191,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132723946</v>
+        <v>132724043</v>
       </c>
       <c r="B37" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>870305</v>
+        <v>870268</v>
       </c>
       <c r="R37" t="n">
-        <v>7311691</v>
+        <v>7311645</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4288,32 +4288,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132724043</v>
+        <v>132723946</v>
       </c>
       <c r="B38" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>870268</v>
+        <v>870305</v>
       </c>
       <c r="R38" t="n">
-        <v>7311645</v>
+        <v>7311691</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4676,32 +4676,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132723940</v>
+        <v>132724033</v>
       </c>
       <c r="B42" t="n">
-        <v>106243</v>
+        <v>99130</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870139</v>
+        <v>870089</v>
       </c>
       <c r="R42" t="n">
-        <v>7311657</v>
+        <v>7311673</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4773,32 +4773,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132724033</v>
+        <v>132723940</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>106243</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870089</v>
+        <v>870139</v>
       </c>
       <c r="R43" t="n">
-        <v>7311673</v>
+        <v>7311657</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132723959</v>
+        <v>132724010</v>
       </c>
       <c r="B47" t="n">
-        <v>92646</v>
+        <v>99130</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5177,37 +5177,38 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>870212</v>
+        <v>870185</v>
       </c>
       <c r="R47" t="n">
-        <v>7311654</v>
+        <v>7311680</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5240,11 +5241,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gren på granlåga.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5272,45 +5268,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132723964</v>
+        <v>132723959</v>
       </c>
       <c r="B48" t="n">
-        <v>57955</v>
+        <v>92646</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>67</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>870194</v>
+        <v>870212</v>
       </c>
       <c r="R48" t="n">
-        <v>7311653</v>
+        <v>7311654</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5345,12 +5344,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gren på granlåga.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5369,49 +5374,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132724010</v>
+        <v>132723964</v>
       </c>
       <c r="B49" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>870185</v>
+        <v>870194</v>
       </c>
       <c r="R49" t="n">
-        <v>7311680</v>
+        <v>7311653</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5452,7 +5453,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5568,49 +5568,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132724019</v>
+        <v>132723983</v>
       </c>
       <c r="B51" t="n">
-        <v>99130</v>
+        <v>99165</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>870221</v>
+        <v>870255</v>
       </c>
       <c r="R51" t="n">
-        <v>7311678</v>
+        <v>7311639</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5643,6 +5647,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5670,53 +5679,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132723983</v>
+        <v>132724019</v>
       </c>
       <c r="B52" t="n">
-        <v>99165</v>
+        <v>99130</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>870255</v>
+        <v>870221</v>
       </c>
       <c r="R52" t="n">
-        <v>7311639</v>
+        <v>7311678</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5749,11 +5754,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5883,7 +5883,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132724027</v>
+        <v>132724022</v>
       </c>
       <c r="B54" t="n">
         <v>99130</v>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>870230</v>
+        <v>870153</v>
       </c>
       <c r="R54" t="n">
-        <v>7311672</v>
+        <v>7311648</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132724022</v>
+        <v>132724021</v>
       </c>
       <c r="B55" t="n">
         <v>99130</v>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>870153</v>
+        <v>870163</v>
       </c>
       <c r="R55" t="n">
-        <v>7311648</v>
+        <v>7311664</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6087,7 +6087,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132724021</v>
+        <v>132724027</v>
       </c>
       <c r="B56" t="n">
         <v>99130</v>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>870163</v>
+        <v>870230</v>
       </c>
       <c r="R56" t="n">
-        <v>7311664</v>
+        <v>7311672</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6189,32 +6189,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132723952</v>
+        <v>132723939</v>
       </c>
       <c r="B57" t="n">
-        <v>91918</v>
+        <v>106243</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>870242</v>
+        <v>870106</v>
       </c>
       <c r="R57" t="n">
-        <v>7311674</v>
+        <v>7311664</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6286,32 +6286,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132723939</v>
+        <v>132723952</v>
       </c>
       <c r="B58" t="n">
-        <v>106243</v>
+        <v>91918</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6321,10 +6321,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>870106</v>
+        <v>870242</v>
       </c>
       <c r="R58" t="n">
-        <v>7311664</v>
+        <v>7311674</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -2984,49 +2984,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132724026</v>
+        <v>132723951</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>870175</v>
+        <v>870232</v>
       </c>
       <c r="R25" t="n">
-        <v>7311661</v>
+        <v>7311643</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3067,7 +3063,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3086,10 +3081,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132723942</v>
+        <v>132723980</v>
       </c>
       <c r="B26" t="n">
-        <v>106243</v>
+        <v>57148</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3097,21 +3092,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221725</v>
+        <v>102613</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3121,10 +3116,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>870192</v>
+        <v>870050</v>
       </c>
       <c r="R26" t="n">
-        <v>7311681</v>
+        <v>7311668</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3183,53 +3178,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132724024</v>
+        <v>132723942</v>
       </c>
       <c r="B27" t="n">
-        <v>99130</v>
+        <v>106243</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>870184</v>
+        <v>870192</v>
       </c>
       <c r="R27" t="n">
-        <v>7311672</v>
+        <v>7311681</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3270,7 +3257,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3289,45 +3275,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132723951</v>
+        <v>132724024</v>
       </c>
       <c r="B28" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>870232</v>
+        <v>870184</v>
       </c>
       <c r="R28" t="n">
-        <v>7311643</v>
+        <v>7311672</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3368,6 +3362,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3386,45 +3381,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132723980</v>
+        <v>132724026</v>
       </c>
       <c r="B29" t="n">
-        <v>57148</v>
+        <v>99130</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870050</v>
+        <v>870175</v>
       </c>
       <c r="R29" t="n">
-        <v>7311668</v>
+        <v>7311661</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3465,6 +3464,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3483,10 +3483,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132723958</v>
+        <v>132724015</v>
       </c>
       <c r="B30" t="n">
-        <v>92646</v>
+        <v>99130</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3494,34 +3494,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>870140</v>
+        <v>870248</v>
       </c>
       <c r="R30" t="n">
-        <v>7311665</v>
+        <v>7311676</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3562,6 +3566,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3580,45 +3585,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132723948</v>
+        <v>132724023</v>
       </c>
       <c r="B31" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>870106</v>
+        <v>870206</v>
       </c>
       <c r="R31" t="n">
-        <v>7311660</v>
+        <v>7311679</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3659,6 +3668,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3677,10 +3687,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132724015</v>
+        <v>132723958</v>
       </c>
       <c r="B32" t="n">
-        <v>99130</v>
+        <v>92646</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3688,38 +3698,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>870248</v>
+        <v>870140</v>
       </c>
       <c r="R32" t="n">
-        <v>7311676</v>
+        <v>7311665</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3760,7 +3766,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3779,49 +3784,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132724023</v>
+        <v>132723948</v>
       </c>
       <c r="B33" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>870206</v>
+        <v>870106</v>
       </c>
       <c r="R33" t="n">
-        <v>7311679</v>
+        <v>7311660</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3862,7 +3863,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3881,53 +3881,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132723984</v>
+        <v>132724042</v>
       </c>
       <c r="B34" t="n">
-        <v>99165</v>
+        <v>92338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219874</v>
+        <v>6040186</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>870326</v>
+        <v>870261</v>
       </c>
       <c r="R34" t="n">
-        <v>7311673</v>
+        <v>7311655</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3960,11 +3956,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3992,10 +3983,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132723941</v>
+        <v>132723984</v>
       </c>
       <c r="B35" t="n">
-        <v>106243</v>
+        <v>99165</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4003,34 +3994,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>870223</v>
+        <v>870326</v>
       </c>
       <c r="R35" t="n">
-        <v>7311680</v>
+        <v>7311673</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4065,12 +4064,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4089,49 +4094,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132724042</v>
+        <v>132723941</v>
       </c>
       <c r="B36" t="n">
-        <v>92338</v>
+        <v>106243</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6040186</v>
+        <v>221725</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870261</v>
+        <v>870223</v>
       </c>
       <c r="R36" t="n">
-        <v>7311655</v>
+        <v>7311680</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4172,7 +4173,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4385,10 +4385,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132723957</v>
+        <v>132723977</v>
       </c>
       <c r="B39" t="n">
-        <v>80467</v>
+        <v>97995</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>870341</v>
+        <v>870291</v>
       </c>
       <c r="R39" t="n">
-        <v>7311668</v>
+        <v>7311643</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132723985</v>
+        <v>132723940</v>
       </c>
       <c r="B40" t="n">
-        <v>99165</v>
+        <v>106243</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219874</v>
+        <v>221725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>870161</v>
+        <v>870139</v>
       </c>
       <c r="R40" t="n">
-        <v>7311671</v>
+        <v>7311657</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4579,10 +4579,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132723977</v>
+        <v>132723943</v>
       </c>
       <c r="B41" t="n">
-        <v>97995</v>
+        <v>106243</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,21 +4590,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>870291</v>
+        <v>870194</v>
       </c>
       <c r="R41" t="n">
-        <v>7311643</v>
+        <v>7311676</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4676,32 +4676,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132724033</v>
+        <v>132723985</v>
       </c>
       <c r="B42" t="n">
-        <v>99130</v>
+        <v>99165</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870089</v>
+        <v>870161</v>
       </c>
       <c r="R42" t="n">
-        <v>7311673</v>
+        <v>7311671</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4773,32 +4773,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132723940</v>
+        <v>132724033</v>
       </c>
       <c r="B43" t="n">
-        <v>106243</v>
+        <v>99130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870139</v>
+        <v>870089</v>
       </c>
       <c r="R43" t="n">
-        <v>7311657</v>
+        <v>7311673</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132723943</v>
+        <v>132723957</v>
       </c>
       <c r="B44" t="n">
-        <v>106243</v>
+        <v>80467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>870194</v>
+        <v>870341</v>
       </c>
       <c r="R44" t="n">
-        <v>7311676</v>
+        <v>7311668</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132723966</v>
+        <v>132724032</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870207</v>
+        <v>870091</v>
       </c>
       <c r="R3" t="n">
-        <v>7311650</v>
+        <v>7311673</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132724032</v>
+        <v>132723966</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870091</v>
+        <v>870207</v>
       </c>
       <c r="R4" t="n">
-        <v>7311673</v>
+        <v>7311650</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132723950</v>
+        <v>132724035</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>57136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>870220</v>
+        <v>870226</v>
       </c>
       <c r="R6" t="n">
-        <v>7311651</v>
+        <v>7311649</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132724008</v>
+        <v>132723960</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>92646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,38 +1186,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870160</v>
+        <v>870208</v>
       </c>
       <c r="R7" t="n">
-        <v>7311638</v>
+        <v>7311661</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1258,7 +1254,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1277,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132723960</v>
+        <v>132723950</v>
       </c>
       <c r="B8" t="n">
-        <v>92646</v>
+        <v>91881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>870208</v>
+        <v>870220</v>
       </c>
       <c r="R8" t="n">
-        <v>7311661</v>
+        <v>7311651</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1374,45 +1369,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132724035</v>
+        <v>132724008</v>
       </c>
       <c r="B9" t="n">
-        <v>57136</v>
+        <v>99130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>870226</v>
+        <v>870160</v>
       </c>
       <c r="R9" t="n">
-        <v>7311649</v>
+        <v>7311638</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1453,6 +1452,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -4385,10 +4385,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132723977</v>
+        <v>132723957</v>
       </c>
       <c r="B39" t="n">
-        <v>97995</v>
+        <v>80467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>870291</v>
+        <v>870341</v>
       </c>
       <c r="R39" t="n">
-        <v>7311643</v>
+        <v>7311668</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132723940</v>
+        <v>132723985</v>
       </c>
       <c r="B40" t="n">
-        <v>106243</v>
+        <v>99165</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>870139</v>
+        <v>870161</v>
       </c>
       <c r="R40" t="n">
-        <v>7311657</v>
+        <v>7311671</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4579,10 +4579,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132723943</v>
+        <v>132723977</v>
       </c>
       <c r="B41" t="n">
-        <v>106243</v>
+        <v>97995</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,21 +4590,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>870194</v>
+        <v>870291</v>
       </c>
       <c r="R41" t="n">
-        <v>7311676</v>
+        <v>7311643</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4676,32 +4676,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132723985</v>
+        <v>132724033</v>
       </c>
       <c r="B42" t="n">
-        <v>99165</v>
+        <v>99130</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870161</v>
+        <v>870089</v>
       </c>
       <c r="R42" t="n">
-        <v>7311671</v>
+        <v>7311673</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4773,32 +4773,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132724033</v>
+        <v>132723940</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>106243</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870089</v>
+        <v>870139</v>
       </c>
       <c r="R43" t="n">
-        <v>7311673</v>
+        <v>7311657</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132723957</v>
+        <v>132723943</v>
       </c>
       <c r="B44" t="n">
-        <v>80467</v>
+        <v>106243</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>870341</v>
+        <v>870194</v>
       </c>
       <c r="R44" t="n">
-        <v>7311668</v>
+        <v>7311676</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5781,7 +5781,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132724011</v>
+        <v>132724022</v>
       </c>
       <c r="B53" t="n">
         <v>99130</v>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>870148</v>
+        <v>870153</v>
       </c>
       <c r="R53" t="n">
-        <v>7311649</v>
+        <v>7311648</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132724022</v>
+        <v>132724011</v>
       </c>
       <c r="B54" t="n">
         <v>99130</v>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>870153</v>
+        <v>870148</v>
       </c>
       <c r="R54" t="n">
-        <v>7311648</v>
+        <v>7311649</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132724021</v>
+        <v>132724027</v>
       </c>
       <c r="B55" t="n">
         <v>99130</v>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>870163</v>
+        <v>870230</v>
       </c>
       <c r="R55" t="n">
-        <v>7311664</v>
+        <v>7311672</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6087,7 +6087,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132724027</v>
+        <v>132724021</v>
       </c>
       <c r="B56" t="n">
         <v>99130</v>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>870230</v>
+        <v>870163</v>
       </c>
       <c r="R56" t="n">
-        <v>7311672</v>
+        <v>7311664</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132724032</v>
+        <v>132723966</v>
       </c>
       <c r="B3" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870091</v>
+        <v>870207</v>
       </c>
       <c r="R3" t="n">
-        <v>7311673</v>
+        <v>7311650</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132723966</v>
+        <v>132724032</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870207</v>
+        <v>870091</v>
       </c>
       <c r="R4" t="n">
-        <v>7311650</v>
+        <v>7311673</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132723966</v>
+        <v>132724032</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>99130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870207</v>
+        <v>870091</v>
       </c>
       <c r="R3" t="n">
-        <v>7311650</v>
+        <v>7311673</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132724032</v>
+        <v>132723966</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870091</v>
+        <v>870207</v>
       </c>
       <c r="R4" t="n">
-        <v>7311673</v>
+        <v>7311650</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132724035</v>
+        <v>132723950</v>
       </c>
       <c r="B6" t="n">
-        <v>57136</v>
+        <v>91881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>870226</v>
+        <v>870220</v>
       </c>
       <c r="R6" t="n">
-        <v>7311649</v>
+        <v>7311651</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132723960</v>
+        <v>132724008</v>
       </c>
       <c r="B7" t="n">
-        <v>92646</v>
+        <v>99130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,34 +1186,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870208</v>
+        <v>870160</v>
       </c>
       <c r="R7" t="n">
-        <v>7311661</v>
+        <v>7311638</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1254,6 +1258,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1272,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132723950</v>
+        <v>132723960</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>92646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>870220</v>
+        <v>870208</v>
       </c>
       <c r="R8" t="n">
-        <v>7311651</v>
+        <v>7311661</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1369,49 +1374,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132724008</v>
+        <v>132724035</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>57136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>870160</v>
+        <v>870226</v>
       </c>
       <c r="R9" t="n">
-        <v>7311638</v>
+        <v>7311649</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1452,7 +1453,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -2186,32 +2186,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132723947</v>
+        <v>132724029</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>870140</v>
+        <v>870105</v>
       </c>
       <c r="R17" t="n">
-        <v>7311665</v>
+        <v>7311661</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2259,12 +2259,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>5 dm2.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2283,7 +2289,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132723949</v>
+        <v>132723947</v>
       </c>
       <c r="B18" t="n">
         <v>91881</v>
@@ -2318,10 +2324,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>870194</v>
+        <v>870140</v>
       </c>
       <c r="R18" t="n">
-        <v>7311657</v>
+        <v>7311665</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2380,32 +2386,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132724029</v>
+        <v>132723949</v>
       </c>
       <c r="B19" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2415,10 +2421,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>870105</v>
+        <v>870194</v>
       </c>
       <c r="R19" t="n">
-        <v>7311661</v>
+        <v>7311657</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2453,18 +2459,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>5 dm2.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2984,45 +2984,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132723951</v>
+        <v>132724026</v>
       </c>
       <c r="B25" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>870232</v>
+        <v>870175</v>
       </c>
       <c r="R25" t="n">
-        <v>7311643</v>
+        <v>7311661</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3063,6 +3067,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3081,10 +3086,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132723980</v>
+        <v>132723942</v>
       </c>
       <c r="B26" t="n">
-        <v>57148</v>
+        <v>106243</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,21 +3097,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102613</v>
+        <v>221725</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3116,10 +3121,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>870050</v>
+        <v>870192</v>
       </c>
       <c r="R26" t="n">
-        <v>7311668</v>
+        <v>7311681</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3178,45 +3183,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132723942</v>
+        <v>132724024</v>
       </c>
       <c r="B27" t="n">
-        <v>106243</v>
+        <v>99130</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>870192</v>
+        <v>870184</v>
       </c>
       <c r="R27" t="n">
-        <v>7311681</v>
+        <v>7311672</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3257,6 +3270,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3275,53 +3289,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132724024</v>
+        <v>132723951</v>
       </c>
       <c r="B28" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>870184</v>
+        <v>870232</v>
       </c>
       <c r="R28" t="n">
-        <v>7311672</v>
+        <v>7311643</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3362,7 +3368,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3381,49 +3386,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132724026</v>
+        <v>132723980</v>
       </c>
       <c r="B29" t="n">
-        <v>99130</v>
+        <v>57148</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870175</v>
+        <v>870050</v>
       </c>
       <c r="R29" t="n">
-        <v>7311661</v>
+        <v>7311668</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3464,7 +3465,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3881,49 +3881,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132724042</v>
+        <v>132723984</v>
       </c>
       <c r="B34" t="n">
-        <v>92338</v>
+        <v>99165</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6040186</v>
+        <v>219874</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>870261</v>
+        <v>870326</v>
       </c>
       <c r="R34" t="n">
-        <v>7311655</v>
+        <v>7311673</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3956,6 +3960,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3983,10 +3992,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132723984</v>
+        <v>132723941</v>
       </c>
       <c r="B35" t="n">
-        <v>99165</v>
+        <v>106243</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3994,42 +4003,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219874</v>
+        <v>221725</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>870326</v>
+        <v>870223</v>
       </c>
       <c r="R35" t="n">
-        <v>7311673</v>
+        <v>7311680</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4064,18 +4065,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4094,45 +4089,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132723941</v>
+        <v>132724042</v>
       </c>
       <c r="B36" t="n">
-        <v>106243</v>
+        <v>92338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221725</v>
+        <v>6040186</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870223</v>
+        <v>870261</v>
       </c>
       <c r="R36" t="n">
-        <v>7311680</v>
+        <v>7311655</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4173,6 +4172,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4385,10 +4385,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132723957</v>
+        <v>132723977</v>
       </c>
       <c r="B39" t="n">
-        <v>80467</v>
+        <v>97995</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>870341</v>
+        <v>870291</v>
       </c>
       <c r="R39" t="n">
-        <v>7311668</v>
+        <v>7311643</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132723985</v>
+        <v>132723940</v>
       </c>
       <c r="B40" t="n">
-        <v>99165</v>
+        <v>106243</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219874</v>
+        <v>221725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>870161</v>
+        <v>870139</v>
       </c>
       <c r="R40" t="n">
-        <v>7311671</v>
+        <v>7311657</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4579,10 +4579,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132723977</v>
+        <v>132723943</v>
       </c>
       <c r="B41" t="n">
-        <v>97995</v>
+        <v>106243</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4590,21 +4590,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>870291</v>
+        <v>870194</v>
       </c>
       <c r="R41" t="n">
-        <v>7311643</v>
+        <v>7311676</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4676,32 +4676,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132724033</v>
+        <v>132723985</v>
       </c>
       <c r="B42" t="n">
-        <v>99130</v>
+        <v>99165</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870089</v>
+        <v>870161</v>
       </c>
       <c r="R42" t="n">
-        <v>7311673</v>
+        <v>7311671</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4773,32 +4773,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132723940</v>
+        <v>132724033</v>
       </c>
       <c r="B43" t="n">
-        <v>106243</v>
+        <v>99130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870139</v>
+        <v>870089</v>
       </c>
       <c r="R43" t="n">
-        <v>7311657</v>
+        <v>7311673</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132723943</v>
+        <v>132723957</v>
       </c>
       <c r="B44" t="n">
-        <v>106243</v>
+        <v>80467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>870194</v>
+        <v>870341</v>
       </c>
       <c r="R44" t="n">
-        <v>7311676</v>
+        <v>7311668</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5781,7 +5781,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132724022</v>
+        <v>132724011</v>
       </c>
       <c r="B53" t="n">
         <v>99130</v>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>870153</v>
+        <v>870148</v>
       </c>
       <c r="R53" t="n">
-        <v>7311648</v>
+        <v>7311649</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132724011</v>
+        <v>132724022</v>
       </c>
       <c r="B54" t="n">
         <v>99130</v>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>870148</v>
+        <v>870153</v>
       </c>
       <c r="R54" t="n">
-        <v>7311649</v>
+        <v>7311648</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132724027</v>
+        <v>132724021</v>
       </c>
       <c r="B55" t="n">
         <v>99130</v>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>870230</v>
+        <v>870163</v>
       </c>
       <c r="R55" t="n">
-        <v>7311672</v>
+        <v>7311664</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6087,7 +6087,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132724021</v>
+        <v>132724027</v>
       </c>
       <c r="B56" t="n">
         <v>99130</v>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>870163</v>
+        <v>870230</v>
       </c>
       <c r="R56" t="n">
-        <v>7311664</v>
+        <v>7311672</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132724032</v>
+        <v>132723966</v>
       </c>
       <c r="B3" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870091</v>
+        <v>870207</v>
       </c>
       <c r="R3" t="n">
-        <v>7311673</v>
+        <v>7311650</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132723966</v>
+        <v>132724032</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>99132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870207</v>
+        <v>870091</v>
       </c>
       <c r="R4" t="n">
-        <v>7311650</v>
+        <v>7311673</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +984,7 @@
         <v>132723979</v>
       </c>
       <c r="B5" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132723950</v>
+        <v>132723960</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>92648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>870220</v>
+        <v>870208</v>
       </c>
       <c r="R6" t="n">
-        <v>7311651</v>
+        <v>7311661</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,49 +1175,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132724008</v>
+        <v>132724035</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>57136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870160</v>
+        <v>870226</v>
       </c>
       <c r="R7" t="n">
-        <v>7311638</v>
+        <v>7311649</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1258,7 +1254,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1277,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132723960</v>
+        <v>132723950</v>
       </c>
       <c r="B8" t="n">
-        <v>92646</v>
+        <v>91883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>870208</v>
+        <v>870220</v>
       </c>
       <c r="R8" t="n">
-        <v>7311661</v>
+        <v>7311651</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1374,45 +1369,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132724035</v>
+        <v>132724008</v>
       </c>
       <c r="B9" t="n">
-        <v>57136</v>
+        <v>99132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>870226</v>
+        <v>870160</v>
       </c>
       <c r="R9" t="n">
-        <v>7311649</v>
+        <v>7311638</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1453,6 +1452,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1471,45 +1471,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132724048</v>
+        <v>132724009</v>
       </c>
       <c r="B10" t="n">
-        <v>78736</v>
+        <v>99132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>870221</v>
+        <v>870145</v>
       </c>
       <c r="R10" t="n">
-        <v>7311646</v>
+        <v>7311659</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1544,11 +1548,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1558,21 +1557,6 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1589,45 +1573,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132723968</v>
+        <v>132724013</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>99132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>870266</v>
+        <v>870190</v>
       </c>
       <c r="R11" t="n">
-        <v>7311659</v>
+        <v>7311676</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1668,6 +1656,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1686,49 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132724009</v>
+        <v>132724048</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>78737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>870145</v>
+        <v>870221</v>
       </c>
       <c r="R12" t="n">
-        <v>7311659</v>
+        <v>7311646</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1763,6 +1748,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1772,6 +1762,21 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1788,49 +1793,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132724013</v>
+        <v>132723968</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>870190</v>
+        <v>870266</v>
       </c>
       <c r="R13" t="n">
-        <v>7311676</v>
+        <v>7311659</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1871,7 +1872,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1890,32 +1890,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132723962</v>
+        <v>132723938</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>106245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>870045</v>
+        <v>870177</v>
       </c>
       <c r="R14" t="n">
-        <v>7311671</v>
+        <v>7311649</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1990,7 +1990,7 @@
         <v>132724030</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2089,32 +2089,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132723938</v>
+        <v>132723962</v>
       </c>
       <c r="B16" t="n">
-        <v>106243</v>
+        <v>57955</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>870177</v>
+        <v>870045</v>
       </c>
       <c r="R16" t="n">
-        <v>7311649</v>
+        <v>7311671</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2186,32 +2186,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132724029</v>
+        <v>132723947</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>91883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>870105</v>
+        <v>870140</v>
       </c>
       <c r="R17" t="n">
-        <v>7311661</v>
+        <v>7311665</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2259,18 +2259,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>5 dm2.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2289,10 +2283,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132723947</v>
+        <v>132723949</v>
       </c>
       <c r="B18" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,10 +2318,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>870140</v>
+        <v>870194</v>
       </c>
       <c r="R18" t="n">
-        <v>7311665</v>
+        <v>7311657</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2386,32 +2380,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132723949</v>
+        <v>132724029</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
+        <v>99132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2421,10 +2415,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>870194</v>
+        <v>870105</v>
       </c>
       <c r="R19" t="n">
-        <v>7311657</v>
+        <v>7311661</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2459,12 +2453,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>5 dm2.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>132724046</v>
       </c>
       <c r="B20" t="n">
-        <v>93242</v>
+        <v>93244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>132724012</v>
       </c>
       <c r="B22" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>132724031</v>
       </c>
       <c r="B23" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>132723986</v>
       </c>
       <c r="B24" t="n">
-        <v>99165</v>
+        <v>99167</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2984,49 +2984,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132724026</v>
+        <v>132723951</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>91883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>870175</v>
+        <v>870232</v>
       </c>
       <c r="R25" t="n">
-        <v>7311661</v>
+        <v>7311643</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3067,7 +3063,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3089,7 +3084,7 @@
         <v>132723942</v>
       </c>
       <c r="B26" t="n">
-        <v>106243</v>
+        <v>106245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3183,53 +3178,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132724024</v>
+        <v>132723980</v>
       </c>
       <c r="B27" t="n">
-        <v>99130</v>
+        <v>57148</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>870184</v>
+        <v>870050</v>
       </c>
       <c r="R27" t="n">
-        <v>7311672</v>
+        <v>7311668</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3270,7 +3257,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3289,45 +3275,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132723951</v>
+        <v>132724024</v>
       </c>
       <c r="B28" t="n">
-        <v>91881</v>
+        <v>99132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>870232</v>
+        <v>870184</v>
       </c>
       <c r="R28" t="n">
-        <v>7311643</v>
+        <v>7311672</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3368,6 +3362,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3386,45 +3381,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132723980</v>
+        <v>132724026</v>
       </c>
       <c r="B29" t="n">
-        <v>57148</v>
+        <v>99132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870050</v>
+        <v>870175</v>
       </c>
       <c r="R29" t="n">
-        <v>7311668</v>
+        <v>7311661</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3465,6 +3464,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3483,10 +3483,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132724015</v>
+        <v>132723958</v>
       </c>
       <c r="B30" t="n">
-        <v>99130</v>
+        <v>92648</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3494,38 +3494,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>67</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>870248</v>
+        <v>870140</v>
       </c>
       <c r="R30" t="n">
-        <v>7311676</v>
+        <v>7311665</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3566,7 +3562,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3585,10 +3580,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132724023</v>
+        <v>132724015</v>
       </c>
       <c r="B31" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3615,7 +3610,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3624,10 +3619,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>870206</v>
+        <v>870248</v>
       </c>
       <c r="R31" t="n">
-        <v>7311679</v>
+        <v>7311676</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3687,10 +3682,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132723958</v>
+        <v>132724023</v>
       </c>
       <c r="B32" t="n">
-        <v>92646</v>
+        <v>99132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3698,34 +3693,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>870140</v>
+        <v>870206</v>
       </c>
       <c r="R32" t="n">
-        <v>7311665</v>
+        <v>7311679</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3766,6 +3765,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>132723948</v>
       </c>
       <c r="B33" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132723984</v>
+        <v>132723941</v>
       </c>
       <c r="B34" t="n">
-        <v>99165</v>
+        <v>106245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3892,42 +3892,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219874</v>
+        <v>221725</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>870326</v>
+        <v>870223</v>
       </c>
       <c r="R34" t="n">
-        <v>7311673</v>
+        <v>7311680</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3962,18 +3954,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3992,45 +3978,49 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132723941</v>
+        <v>132724042</v>
       </c>
       <c r="B35" t="n">
-        <v>106243</v>
+        <v>92340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221725</v>
+        <v>6040186</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>870223</v>
+        <v>870261</v>
       </c>
       <c r="R35" t="n">
-        <v>7311680</v>
+        <v>7311655</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4071,6 +4061,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4089,10 +4080,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132724042</v>
+        <v>132724043</v>
       </c>
       <c r="B36" t="n">
-        <v>92338</v>
+        <v>79334</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4100,38 +4091,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870261</v>
+        <v>870268</v>
       </c>
       <c r="R36" t="n">
-        <v>7311655</v>
+        <v>7311645</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4172,7 +4159,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4191,32 +4177,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132724043</v>
+        <v>132723946</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>91883</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4226,10 +4212,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>870268</v>
+        <v>870305</v>
       </c>
       <c r="R37" t="n">
-        <v>7311645</v>
+        <v>7311691</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4288,10 +4274,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132723946</v>
+        <v>132723984</v>
       </c>
       <c r="B38" t="n">
-        <v>91881</v>
+        <v>99167</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4299,34 +4285,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>219874</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>870305</v>
+        <v>870326</v>
       </c>
       <c r="R38" t="n">
-        <v>7311691</v>
+        <v>7311673</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4361,12 +4355,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4385,10 +4385,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132723977</v>
+        <v>132723957</v>
       </c>
       <c r="B39" t="n">
-        <v>97995</v>
+        <v>80468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>870291</v>
+        <v>870341</v>
       </c>
       <c r="R39" t="n">
-        <v>7311643</v>
+        <v>7311668</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132723940</v>
+        <v>132723985</v>
       </c>
       <c r="B40" t="n">
-        <v>106243</v>
+        <v>99167</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>870139</v>
+        <v>870161</v>
       </c>
       <c r="R40" t="n">
-        <v>7311657</v>
+        <v>7311671</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4579,32 +4579,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132723943</v>
+        <v>132724033</v>
       </c>
       <c r="B41" t="n">
-        <v>106243</v>
+        <v>99132</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>870194</v>
+        <v>870089</v>
       </c>
       <c r="R41" t="n">
-        <v>7311676</v>
+        <v>7311673</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132723985</v>
+        <v>132723940</v>
       </c>
       <c r="B42" t="n">
-        <v>99165</v>
+        <v>106245</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>221725</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870161</v>
+        <v>870139</v>
       </c>
       <c r="R42" t="n">
-        <v>7311671</v>
+        <v>7311657</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4773,32 +4773,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132724033</v>
+        <v>132723943</v>
       </c>
       <c r="B43" t="n">
-        <v>99130</v>
+        <v>106245</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870089</v>
+        <v>870194</v>
       </c>
       <c r="R43" t="n">
-        <v>7311673</v>
+        <v>7311676</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132723957</v>
+        <v>132723977</v>
       </c>
       <c r="B44" t="n">
-        <v>80467</v>
+        <v>97997</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>870341</v>
+        <v>870291</v>
       </c>
       <c r="R44" t="n">
-        <v>7311668</v>
+        <v>7311643</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4967,49 +4967,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132724020</v>
+        <v>132723963</v>
       </c>
       <c r="B45" t="n">
-        <v>99130</v>
+        <v>57955</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>870092</v>
+        <v>870057</v>
       </c>
       <c r="R45" t="n">
-        <v>7311665</v>
+        <v>7311663</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5050,7 +5046,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5069,45 +5064,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132723963</v>
+        <v>132724020</v>
       </c>
       <c r="B46" t="n">
-        <v>57955</v>
+        <v>99132</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>870057</v>
+        <v>870092</v>
       </c>
       <c r="R46" t="n">
-        <v>7311663</v>
+        <v>7311665</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5148,6 +5147,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>132724010</v>
       </c>
       <c r="B47" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>132723959</v>
       </c>
       <c r="B48" t="n">
-        <v>92646</v>
+        <v>92648</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5471,10 +5471,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132723954</v>
+        <v>132723983</v>
       </c>
       <c r="B50" t="n">
-        <v>92641</v>
+        <v>99167</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5482,34 +5482,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>219874</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>870345</v>
+        <v>870255</v>
       </c>
       <c r="R50" t="n">
-        <v>7311658</v>
+        <v>7311639</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5544,12 +5552,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5568,10 +5582,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132723983</v>
+        <v>132723954</v>
       </c>
       <c r="B51" t="n">
-        <v>99165</v>
+        <v>92643</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5579,42 +5593,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219874</v>
+        <v>3298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>870255</v>
+        <v>870345</v>
       </c>
       <c r="R51" t="n">
-        <v>7311639</v>
+        <v>7311658</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5649,18 +5655,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5682,7 +5682,7 @@
         <v>132724019</v>
       </c>
       <c r="B52" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>132724011</v>
       </c>
       <c r="B53" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132724022</v>
+        <v>132724027</v>
       </c>
       <c r="B54" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>870153</v>
+        <v>870230</v>
       </c>
       <c r="R54" t="n">
-        <v>7311648</v>
+        <v>7311672</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5985,10 +5985,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132724021</v>
+        <v>132724022</v>
       </c>
       <c r="B55" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>870163</v>
+        <v>870153</v>
       </c>
       <c r="R55" t="n">
-        <v>7311664</v>
+        <v>7311648</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6087,10 +6087,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132724027</v>
+        <v>132724021</v>
       </c>
       <c r="B56" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>870230</v>
+        <v>870163</v>
       </c>
       <c r="R56" t="n">
-        <v>7311672</v>
+        <v>7311664</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6189,45 +6189,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132723939</v>
+        <v>132724016</v>
       </c>
       <c r="B57" t="n">
-        <v>106243</v>
+        <v>99132</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>870106</v>
+        <v>870243</v>
       </c>
       <c r="R57" t="n">
-        <v>7311664</v>
+        <v>7311678</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6268,6 +6272,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6289,7 +6294,7 @@
         <v>132723952</v>
       </c>
       <c r="B58" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6383,49 +6388,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132724016</v>
+        <v>132723939</v>
       </c>
       <c r="B59" t="n">
-        <v>99130</v>
+        <v>106245</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>870243</v>
+        <v>870106</v>
       </c>
       <c r="R59" t="n">
-        <v>7311678</v>
+        <v>7311664</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6466,7 +6467,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>132724028</v>
       </c>
       <c r="B60" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>132724017</v>
       </c>
       <c r="B61" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132723966</v>
+        <v>132723979</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>98003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870207</v>
+        <v>870312</v>
       </c>
       <c r="R3" t="n">
-        <v>7311650</v>
+        <v>7311654</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132724032</v>
+        <v>132723966</v>
       </c>
       <c r="B4" t="n">
-        <v>99132</v>
+        <v>57955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870091</v>
+        <v>870207</v>
       </c>
       <c r="R4" t="n">
-        <v>7311673</v>
+        <v>7311650</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132723979</v>
+        <v>132724032</v>
       </c>
       <c r="B5" t="n">
-        <v>98003</v>
+        <v>99132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>870312</v>
+        <v>870091</v>
       </c>
       <c r="R5" t="n">
-        <v>7311654</v>
+        <v>7311673</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132723960</v>
+        <v>132724035</v>
       </c>
       <c r="B6" t="n">
-        <v>92648</v>
+        <v>57136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>870208</v>
+        <v>870226</v>
       </c>
       <c r="R6" t="n">
-        <v>7311661</v>
+        <v>7311649</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,45 +1175,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132724035</v>
+        <v>132724008</v>
       </c>
       <c r="B7" t="n">
-        <v>57136</v>
+        <v>99132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870226</v>
+        <v>870160</v>
       </c>
       <c r="R7" t="n">
-        <v>7311649</v>
+        <v>7311638</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1254,6 +1258,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1272,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132723950</v>
+        <v>132723960</v>
       </c>
       <c r="B8" t="n">
-        <v>91883</v>
+        <v>92648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>870220</v>
+        <v>870208</v>
       </c>
       <c r="R8" t="n">
-        <v>7311651</v>
+        <v>7311661</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1369,49 +1374,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132724008</v>
+        <v>132723950</v>
       </c>
       <c r="B9" t="n">
-        <v>99132</v>
+        <v>91883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>870160</v>
+        <v>870220</v>
       </c>
       <c r="R9" t="n">
-        <v>7311638</v>
+        <v>7311651</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1452,7 +1453,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1471,46 +1471,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132724009</v>
+        <v>132723968</v>
       </c>
       <c r="B10" t="n">
-        <v>99132</v>
+        <v>57955</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>870145</v>
+        <v>870266</v>
       </c>
       <c r="R10" t="n">
         <v>7311659</v>
@@ -1554,7 +1550,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1573,49 +1568,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132724013</v>
+        <v>132724048</v>
       </c>
       <c r="B11" t="n">
-        <v>99132</v>
+        <v>78737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>870190</v>
+        <v>870221</v>
       </c>
       <c r="R11" t="n">
-        <v>7311676</v>
+        <v>7311646</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1650,6 +1641,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1659,6 +1655,21 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1675,45 +1686,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132724048</v>
+        <v>132724009</v>
       </c>
       <c r="B12" t="n">
-        <v>78737</v>
+        <v>99132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>870221</v>
+        <v>870145</v>
       </c>
       <c r="R12" t="n">
-        <v>7311646</v>
+        <v>7311659</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1748,11 +1763,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1762,21 +1772,6 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1793,45 +1788,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132723968</v>
+        <v>132724013</v>
       </c>
       <c r="B13" t="n">
-        <v>57955</v>
+        <v>99132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>870266</v>
+        <v>870190</v>
       </c>
       <c r="R13" t="n">
-        <v>7311659</v>
+        <v>7311676</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1872,6 +1871,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1890,32 +1890,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132723938</v>
+        <v>132723962</v>
       </c>
       <c r="B14" t="n">
-        <v>106245</v>
+        <v>57955</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221725</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>870177</v>
+        <v>870045</v>
       </c>
       <c r="R14" t="n">
-        <v>7311649</v>
+        <v>7311671</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2089,32 +2089,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132723962</v>
+        <v>132723938</v>
       </c>
       <c r="B16" t="n">
-        <v>57955</v>
+        <v>106245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>870045</v>
+        <v>870177</v>
       </c>
       <c r="R16" t="n">
-        <v>7311671</v>
+        <v>7311649</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -3580,49 +3580,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132724015</v>
+        <v>132723948</v>
       </c>
       <c r="B31" t="n">
-        <v>99132</v>
+        <v>91883</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>870248</v>
+        <v>870106</v>
       </c>
       <c r="R31" t="n">
-        <v>7311676</v>
+        <v>7311660</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3663,7 +3659,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3682,7 +3677,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132724023</v>
+        <v>132724015</v>
       </c>
       <c r="B32" t="n">
         <v>99132</v>
@@ -3712,7 +3707,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3721,10 +3716,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>870206</v>
+        <v>870248</v>
       </c>
       <c r="R32" t="n">
-        <v>7311679</v>
+        <v>7311676</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3784,45 +3779,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132723948</v>
+        <v>132724023</v>
       </c>
       <c r="B33" t="n">
-        <v>91883</v>
+        <v>99132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>870106</v>
+        <v>870206</v>
       </c>
       <c r="R33" t="n">
-        <v>7311660</v>
+        <v>7311679</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3863,6 +3862,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132723985</v>
+        <v>132723940</v>
       </c>
       <c r="B40" t="n">
-        <v>99167</v>
+        <v>106245</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219874</v>
+        <v>221725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>870161</v>
+        <v>870139</v>
       </c>
       <c r="R40" t="n">
-        <v>7311671</v>
+        <v>7311657</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4579,32 +4579,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132724033</v>
+        <v>132723943</v>
       </c>
       <c r="B41" t="n">
-        <v>99132</v>
+        <v>106245</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>870089</v>
+        <v>870194</v>
       </c>
       <c r="R41" t="n">
-        <v>7311673</v>
+        <v>7311676</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132723940</v>
+        <v>132723977</v>
       </c>
       <c r="B42" t="n">
-        <v>106245</v>
+        <v>97997</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870139</v>
+        <v>870291</v>
       </c>
       <c r="R42" t="n">
-        <v>7311657</v>
+        <v>7311643</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132723943</v>
+        <v>132723985</v>
       </c>
       <c r="B43" t="n">
-        <v>106245</v>
+        <v>99167</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4784,21 +4784,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870194</v>
+        <v>870161</v>
       </c>
       <c r="R43" t="n">
-        <v>7311676</v>
+        <v>7311671</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4870,32 +4870,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132723977</v>
+        <v>132724033</v>
       </c>
       <c r="B44" t="n">
-        <v>97997</v>
+        <v>99132</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>870291</v>
+        <v>870089</v>
       </c>
       <c r="R44" t="n">
-        <v>7311643</v>
+        <v>7311673</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5166,49 +5166,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132724010</v>
+        <v>132723964</v>
       </c>
       <c r="B47" t="n">
-        <v>99132</v>
+        <v>57955</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>870185</v>
+        <v>870194</v>
       </c>
       <c r="R47" t="n">
-        <v>7311680</v>
+        <v>7311653</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5249,7 +5245,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5268,10 +5263,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132723959</v>
+        <v>132724010</v>
       </c>
       <c r="B48" t="n">
-        <v>92648</v>
+        <v>99132</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5279,37 +5274,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>870212</v>
+        <v>870185</v>
       </c>
       <c r="R48" t="n">
-        <v>7311654</v>
+        <v>7311680</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5342,11 +5338,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På gren på granlåga.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5374,45 +5365,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132723964</v>
+        <v>132723959</v>
       </c>
       <c r="B49" t="n">
-        <v>57955</v>
+        <v>92648</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>67</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>870194</v>
+        <v>870212</v>
       </c>
       <c r="R49" t="n">
-        <v>7311653</v>
+        <v>7311654</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5447,12 +5441,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gren på granlåga.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6189,49 +6189,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132724016</v>
+        <v>132723952</v>
       </c>
       <c r="B57" t="n">
-        <v>99132</v>
+        <v>91920</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>870243</v>
+        <v>870242</v>
       </c>
       <c r="R57" t="n">
-        <v>7311678</v>
+        <v>7311674</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6272,7 +6268,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6291,45 +6286,49 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132723952</v>
+        <v>132724016</v>
       </c>
       <c r="B58" t="n">
-        <v>91920</v>
+        <v>99132</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>870242</v>
+        <v>870243</v>
       </c>
       <c r="R58" t="n">
-        <v>7311674</v>
+        <v>7311678</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6370,6 +6369,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 956-2026 artfynd.xlsx
+++ b/artfynd/A 956-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110045666</v>
+        <v>132723958</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vikmyran-Storön, Nb</t>
+          <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>870266.363460385</v>
+        <v>870140</v>
       </c>
       <c r="R2" t="n">
-        <v>7311647.298082567</v>
+        <v>7311665</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,54 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132723979</v>
+        <v>132723959</v>
       </c>
       <c r="B3" t="n">
-        <v>98003</v>
+        <v>92201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>870312</v>
+        <v>870212</v>
       </c>
       <c r="R3" t="n">
         <v>7311654</v>
@@ -860,12 +848,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gren på granlåga.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,32 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132723966</v>
+        <v>132723960</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>92201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>67</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>870207</v>
+        <v>870208</v>
       </c>
       <c r="R4" t="n">
-        <v>7311650</v>
+        <v>7311661</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,32 +975,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132724032</v>
+        <v>132723952</v>
       </c>
       <c r="B5" t="n">
-        <v>99132</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>870091</v>
+        <v>870242</v>
       </c>
       <c r="R5" t="n">
-        <v>7311673</v>
+        <v>7311674</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,32 +1072,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132724035</v>
+        <v>132723993</v>
       </c>
       <c r="B6" t="n">
-        <v>57136</v>
+        <v>96410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>870226</v>
+        <v>870257</v>
       </c>
       <c r="R6" t="n">
-        <v>7311649</v>
+        <v>7311684</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,49 +1169,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132724008</v>
+        <v>132723994</v>
       </c>
       <c r="B7" t="n">
-        <v>99132</v>
+        <v>96410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>870160</v>
+        <v>870215</v>
       </c>
       <c r="R7" t="n">
-        <v>7311638</v>
+        <v>7311681</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1258,7 +1248,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1277,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132723960</v>
+        <v>132723995</v>
       </c>
       <c r="B8" t="n">
-        <v>92648</v>
+        <v>96410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>870208</v>
+        <v>870170</v>
       </c>
       <c r="R8" t="n">
-        <v>7311661</v>
+        <v>7311651</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1374,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132723950</v>
+        <v>132723996</v>
       </c>
       <c r="B9" t="n">
-        <v>91883</v>
+        <v>96410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>870220</v>
+        <v>870152</v>
       </c>
       <c r="R9" t="n">
-        <v>7311651</v>
+        <v>7311665</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1471,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132723968</v>
+        <v>132723998</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>96410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2812</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>870266</v>
+        <v>870139</v>
       </c>
       <c r="R10" t="n">
-        <v>7311659</v>
+        <v>7311650</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1568,32 +1557,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132724048</v>
+        <v>132724000</v>
       </c>
       <c r="B11" t="n">
-        <v>78737</v>
+        <v>96410</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>2812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,7 +1592,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>870221</v>
+        <v>870154</v>
       </c>
       <c r="R11" t="n">
         <v>7311646</v>
@@ -1641,35 +1630,14 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1686,49 +1654,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132724009</v>
+        <v>132724001</v>
       </c>
       <c r="B12" t="n">
-        <v>99132</v>
+        <v>96410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>870145</v>
+        <v>870160</v>
       </c>
       <c r="R12" t="n">
-        <v>7311659</v>
+        <v>7311637</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1769,7 +1733,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1788,49 +1751,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132724013</v>
+        <v>132724002</v>
       </c>
       <c r="B13" t="n">
-        <v>99132</v>
+        <v>96410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>870190</v>
+        <v>870255</v>
       </c>
       <c r="R13" t="n">
-        <v>7311676</v>
+        <v>7311642</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1871,7 +1830,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1890,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132723962</v>
+        <v>132724003</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>96410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2812</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1925,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>870045</v>
+        <v>870236</v>
       </c>
       <c r="R14" t="n">
-        <v>7311671</v>
+        <v>7311674</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1987,49 +1945,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132724030</v>
+        <v>132724004</v>
       </c>
       <c r="B15" t="n">
-        <v>99132</v>
+        <v>96410</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>870251</v>
+        <v>870183</v>
       </c>
       <c r="R15" t="n">
-        <v>7311687</v>
+        <v>7311675</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2070,7 +2024,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2089,10 +2042,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132723938</v>
+        <v>132723954</v>
       </c>
       <c r="B16" t="n">
-        <v>106245</v>
+        <v>92199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2053,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2077,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>870177</v>
+        <v>870345</v>
       </c>
       <c r="R16" t="n">
-        <v>7311649</v>
+        <v>7311658</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2186,10 +2139,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132723947</v>
+        <v>132723955</v>
       </c>
       <c r="B17" t="n">
-        <v>91883</v>
+        <v>92199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,21 +2150,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2221,10 +2174,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>870140</v>
+        <v>870259</v>
       </c>
       <c r="R17" t="n">
-        <v>7311665</v>
+        <v>7311693</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2283,10 +2236,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132723949</v>
+        <v>132723946</v>
       </c>
       <c r="B18" t="n">
-        <v>91883</v>
+        <v>91937</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2318,10 +2271,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>870194</v>
+        <v>870305</v>
       </c>
       <c r="R18" t="n">
-        <v>7311657</v>
+        <v>7311691</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2380,32 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132724029</v>
+        <v>132723947</v>
       </c>
       <c r="B19" t="n">
-        <v>99132</v>
+        <v>91937</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2415,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>870105</v>
+        <v>870140</v>
       </c>
       <c r="R19" t="n">
-        <v>7311661</v>
+        <v>7311665</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2453,18 +2406,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>5 dm2.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2483,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132724046</v>
+        <v>132723948</v>
       </c>
       <c r="B20" t="n">
-        <v>93244</v>
+        <v>91937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2494,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2518,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>870273</v>
+        <v>870106</v>
       </c>
       <c r="R20" t="n">
-        <v>7311688</v>
+        <v>7311660</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2556,18 +2503,12 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropp men enbart gran runt om.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2586,32 +2527,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132723969</v>
+        <v>132723949</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>91937</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2621,10 +2562,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>870248</v>
+        <v>870194</v>
       </c>
       <c r="R21" t="n">
-        <v>7311673</v>
+        <v>7311657</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2683,49 +2624,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132724012</v>
+        <v>132723950</v>
       </c>
       <c r="B22" t="n">
-        <v>99132</v>
+        <v>91937</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>870112</v>
+        <v>870220</v>
       </c>
       <c r="R22" t="n">
-        <v>7311656</v>
+        <v>7311651</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2766,7 +2703,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2785,49 +2721,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132724031</v>
+        <v>132723951</v>
       </c>
       <c r="B23" t="n">
-        <v>99132</v>
+        <v>91937</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>870082</v>
+        <v>870232</v>
       </c>
       <c r="R23" t="n">
-        <v>7311662</v>
+        <v>7311643</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2868,7 +2800,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2887,32 +2818,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132723986</v>
+        <v>132724046</v>
       </c>
       <c r="B24" t="n">
-        <v>99167</v>
+        <v>93307</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2922,10 +2853,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>870063</v>
+        <v>870273</v>
       </c>
       <c r="R24" t="n">
-        <v>7311665</v>
+        <v>7311688</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2960,12 +2891,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropp men enbart gran runt om.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2984,32 +2921,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132723951</v>
+        <v>132724043</v>
       </c>
       <c r="B25" t="n">
-        <v>91883</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3019,10 +2956,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>870232</v>
+        <v>870268</v>
       </c>
       <c r="R25" t="n">
-        <v>7311643</v>
+        <v>7311645</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3081,32 +3018,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132723942</v>
+        <v>132724048</v>
       </c>
       <c r="B26" t="n">
-        <v>106245</v>
+        <v>78776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221725</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3116,10 +3053,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>870192</v>
+        <v>870221</v>
       </c>
       <c r="R26" t="n">
-        <v>7311681</v>
+        <v>7311646</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3154,14 +3091,35 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På solexponerad silverlåga av gran lutad mot flyttblock.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3178,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132723980</v>
+        <v>132723957</v>
       </c>
       <c r="B27" t="n">
-        <v>57148</v>
+        <v>80493</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3189,21 +3147,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102613</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3213,7 +3171,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>870050</v>
+        <v>870341</v>
       </c>
       <c r="R27" t="n">
         <v>7311668</v>
@@ -3275,53 +3233,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132724024</v>
+        <v>132723962</v>
       </c>
       <c r="B28" t="n">
-        <v>99132</v>
+        <v>57972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>870184</v>
+        <v>870045</v>
       </c>
       <c r="R28" t="n">
-        <v>7311672</v>
+        <v>7311671</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3362,7 +3312,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3381,49 +3330,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132724026</v>
+        <v>132723963</v>
       </c>
       <c r="B29" t="n">
-        <v>99132</v>
+        <v>57972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>870175</v>
+        <v>870057</v>
       </c>
       <c r="R29" t="n">
-        <v>7311661</v>
+        <v>7311663</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3464,7 +3409,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3483,32 +3427,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132723958</v>
+        <v>132723964</v>
       </c>
       <c r="B30" t="n">
-        <v>92648</v>
+        <v>57972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>67</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3518,10 +3462,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>870140</v>
+        <v>870194</v>
       </c>
       <c r="R30" t="n">
-        <v>7311665</v>
+        <v>7311653</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3580,10 +3524,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132723948</v>
+        <v>132723966</v>
       </c>
       <c r="B31" t="n">
-        <v>91883</v>
+        <v>57972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3591,21 +3535,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3615,10 +3559,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>870106</v>
+        <v>870207</v>
       </c>
       <c r="R31" t="n">
-        <v>7311660</v>
+        <v>7311650</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3677,49 +3621,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132724015</v>
+        <v>132723968</v>
       </c>
       <c r="B32" t="n">
-        <v>99132</v>
+        <v>57972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>870248</v>
+        <v>870266</v>
       </c>
       <c r="R32" t="n">
-        <v>7311676</v>
+        <v>7311659</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3760,7 +3700,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3779,49 +3718,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132724023</v>
+        <v>132723969</v>
       </c>
       <c r="B33" t="n">
-        <v>99132</v>
+        <v>57972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>870206</v>
+        <v>870248</v>
       </c>
       <c r="R33" t="n">
-        <v>7311679</v>
+        <v>7311673</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3862,7 +3797,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3881,10 +3815,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132723941</v>
+        <v>132724047</v>
       </c>
       <c r="B34" t="n">
-        <v>106245</v>
+        <v>5181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3892,21 +3826,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221725</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3916,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>870223</v>
+        <v>870262</v>
       </c>
       <c r="R34" t="n">
-        <v>7311680</v>
+        <v>7311642</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3960,6 +3894,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3978,49 +3913,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132724042</v>
+        <v>132724035</v>
       </c>
       <c r="B35" t="n">
-        <v>92340</v>
+        <v>57153</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6040186</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>870261</v>
+        <v>870226</v>
       </c>
       <c r="R35" t="n">
-        <v>7311655</v>
+        <v>7311649</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4061,7 +3992,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4080,32 +4010,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132724043</v>
+        <v>132723980</v>
       </c>
       <c r="B36" t="n">
-        <v>79334</v>
+        <v>57165</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4115,10 +4045,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>870268</v>
+        <v>870050</v>
       </c>
       <c r="R36" t="n">
-        <v>7311645</v>
+        <v>7311668</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4177,10 +4107,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132723946</v>
+        <v>132723983</v>
       </c>
       <c r="B37" t="n">
-        <v>91883</v>
+        <v>99230</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4188,34 +4118,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>219874</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>870305</v>
+        <v>870255</v>
       </c>
       <c r="R37" t="n">
-        <v>7311691</v>
+        <v>7311639</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4250,12 +4188,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fröställningar</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4277,7 +4221,7 @@
         <v>132723984</v>
       </c>
       <c r="B38" t="n">
-        <v>99167</v>
+        <v>99230</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4385,10 +4329,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132723957</v>
+        <v>132723985</v>
       </c>
       <c r="B39" t="n">
-        <v>80468</v>
+        <v>99230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4396,21 +4340,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4420,10 +4364,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>870341</v>
+        <v>870161</v>
       </c>
       <c r="R39" t="n">
-        <v>7311668</v>
+        <v>7311671</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4482,10 +4426,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132723940</v>
+        <v>132723986</v>
       </c>
       <c r="B40" t="n">
-        <v>106245</v>
+        <v>99230</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4493,21 +4437,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221725</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4517,10 +4461,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>870139</v>
+        <v>870063</v>
       </c>
       <c r="R40" t="n">
-        <v>7311657</v>
+        <v>7311665</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4579,45 +4523,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132723943</v>
+        <v>132724008</v>
       </c>
       <c r="B41" t="n">
-        <v>106245</v>
+        <v>99195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>870194</v>
+        <v>870160</v>
       </c>
       <c r="R41" t="n">
-        <v>7311676</v>
+        <v>7311638</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4658,6 +4606,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4676,45 +4625,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132723977</v>
+        <v>132724009</v>
       </c>
       <c r="B42" t="n">
-        <v>97997</v>
+        <v>99195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>870291</v>
+        <v>870145</v>
       </c>
       <c r="R42" t="n">
-        <v>7311643</v>
+        <v>7311659</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4755,6 +4708,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4773,45 +4727,49 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132723985</v>
+        <v>132724010</v>
       </c>
       <c r="B43" t="n">
-        <v>99167</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>870161</v>
+        <v>870185</v>
       </c>
       <c r="R43" t="n">
-        <v>7311671</v>
+        <v>7311680</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4852,6 +4810,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4870,10 +4829,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132724033</v>
+        <v>132724011</v>
       </c>
       <c r="B44" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4898,17 +4857,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>870089</v>
+        <v>870148</v>
       </c>
       <c r="R44" t="n">
-        <v>7311673</v>
+        <v>7311649</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4949,6 +4912,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4967,45 +4931,49 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132723963</v>
+        <v>132724012</v>
       </c>
       <c r="B45" t="n">
-        <v>57955</v>
+        <v>99195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>870057</v>
+        <v>870112</v>
       </c>
       <c r="R45" t="n">
-        <v>7311663</v>
+        <v>7311656</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5046,6 +5014,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5064,10 +5033,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132724020</v>
+        <v>132724013</v>
       </c>
       <c r="B46" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5094,7 +5063,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>49</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5103,10 +5072,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>870092</v>
+        <v>870190</v>
       </c>
       <c r="R46" t="n">
-        <v>7311665</v>
+        <v>7311676</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5166,45 +5135,49 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132723964</v>
+        <v>132724014</v>
       </c>
       <c r="B47" t="n">
-        <v>57955</v>
+        <v>99195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>870194</v>
+        <v>870102</v>
       </c>
       <c r="R47" t="n">
-        <v>7311653</v>
+        <v>7311639</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5245,6 +5218,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5263,10 +5237,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132724010</v>
+        <v>132724015</v>
       </c>
       <c r="B48" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5293,7 +5267,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5302,10 +5276,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>870185</v>
+        <v>870248</v>
       </c>
       <c r="R48" t="n">
-        <v>7311680</v>
+        <v>7311676</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5365,10 +5339,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132723959</v>
+        <v>132724016</v>
       </c>
       <c r="B49" t="n">
-        <v>92648</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5376,37 +5350,38 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>67</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>870212</v>
+        <v>870243</v>
       </c>
       <c r="R49" t="n">
-        <v>7311654</v>
+        <v>7311678</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5439,11 +5414,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gren på granlåga.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5471,53 +5441,49 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132723983</v>
+        <v>132724017</v>
       </c>
       <c r="B50" t="n">
-        <v>99167</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>41</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>870255</v>
+        <v>870091</v>
       </c>
       <c r="R50" t="n">
-        <v>7311639</v>
+        <v>7311660</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5550,11 +5516,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Fröställningar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5582,45 +5543,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132723954</v>
+        <v>132724019</v>
       </c>
       <c r="B51" t="n">
-        <v>92643</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>870345</v>
+        <v>870221</v>
       </c>
       <c r="R51" t="n">
-        <v>7311658</v>
+        <v>7311678</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5661,6 +5626,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5679,10 +5645,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132724019</v>
+        <v>132724020</v>
       </c>
       <c r="B52" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5709,7 +5675,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5718,10 +5684,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>870221</v>
+        <v>870092</v>
       </c>
       <c r="R52" t="n">
-        <v>7311678</v>
+        <v>7311665</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5781,10 +5747,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132724011</v>
+        <v>132724021</v>
       </c>
       <c r="B53" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5811,7 +5777,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5820,10 +5786,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>870148</v>
+        <v>870163</v>
       </c>
       <c r="R53" t="n">
-        <v>7311649</v>
+        <v>7311664</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5883,10 +5849,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132724027</v>
+        <v>132724022</v>
       </c>
       <c r="B54" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5913,7 +5879,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5922,10 +5888,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>870230</v>
+        <v>870153</v>
       </c>
       <c r="R54" t="n">
-        <v>7311672</v>
+        <v>7311648</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5985,10 +5951,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132724022</v>
+        <v>132724023</v>
       </c>
       <c r="B55" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6015,7 +5981,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6024,10 +5990,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>870153</v>
+        <v>870206</v>
       </c>
       <c r="R55" t="n">
-        <v>7311648</v>
+        <v>7311679</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6087,10 +6053,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132724021</v>
+        <v>132724024</v>
       </c>
       <c r="B56" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6117,19 +6083,23 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>870163</v>
+        <v>870184</v>
       </c>
       <c r="R56" t="n">
-        <v>7311664</v>
+        <v>7311672</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6189,45 +6159,49 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132723952</v>
+        <v>132724026</v>
       </c>
       <c r="B57" t="n">
-        <v>91920</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>870242</v>
+        <v>870175</v>
       </c>
       <c r="R57" t="n">
-        <v>7311674</v>
+        <v>7311661</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6268,6 +6242,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6286,10 +6261,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132724016</v>
+        <v>132724027</v>
       </c>
       <c r="B58" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6316,7 +6291,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6325,10 +6300,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>870243</v>
+        <v>870230</v>
       </c>
       <c r="R58" t="n">
-        <v>7311678</v>
+        <v>7311672</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6388,32 +6363,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132723939</v>
+        <v>132724028</v>
       </c>
       <c r="B59" t="n">
-        <v>106245</v>
+        <v>99195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6423,10 +6398,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>870106</v>
+        <v>870101</v>
       </c>
       <c r="R59" t="n">
-        <v>7311664</v>
+        <v>7311647</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6461,12 +6436,18 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>5 dm2</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6485,10 +6466,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132724028</v>
+        <v>132724029</v>
       </c>
       <c r="B60" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6520,10 +6501,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>870101</v>
+        <v>870105</v>
       </c>
       <c r="R60" t="n">
-        <v>7311647</v>
+        <v>7311661</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6560,7 +6541,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>5 dm2</t>
+          <t>5 dm2.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6588,10 +6569,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132724017</v>
+        <v>132724030</v>
       </c>
       <c r="B61" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6618,7 +6599,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6627,10 +6608,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>870091</v>
+        <v>870251</v>
       </c>
       <c r="R61" t="n">
-        <v>7311660</v>
+        <v>7311687</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6690,45 +6671,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132724047</v>
+        <v>132724031</v>
       </c>
       <c r="B62" t="n">
-        <v>5179</v>
+        <v>99195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skagsudde, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>870262</v>
+        <v>870082</v>
       </c>
       <c r="R62" t="n">
-        <v>7311642</v>
+        <v>7311662</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6785,6 +6770,1477 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132724032</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>870091</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7311673</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132724033</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>870089</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7311673</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132724034</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>870194</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7311688</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132723938</v>
+      </c>
+      <c r="B66" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>870177</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7311649</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132723939</v>
+      </c>
+      <c r="B67" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>870106</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7311664</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132723940</v>
+      </c>
+      <c r="B68" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>870139</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7311657</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132723941</v>
+      </c>
+      <c r="B69" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>870223</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7311680</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>132723942</v>
+      </c>
+      <c r="B70" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>870192</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7311681</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>132723943</v>
+      </c>
+      <c r="B71" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>870194</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7311676</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>132723979</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>870312</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7311654</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>132723977</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>870291</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7311643</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4898872</v>
+      </c>
+      <c r="B74" t="n">
+        <v>100143</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Svartskataudden. 18 km SSV Kalix., Nb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>870093</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7311630</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2012-07-29</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2012-07-29</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>I myr</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>5880978</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99028</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>223572</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Blodnycklar</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. cruenta</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(O F.Müll.) Hyl.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Svartskataudden. 18 km SSV Kalix., Nb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>870093</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7311630</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2012-07-29</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2012-07-29</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>I myr</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>5988675</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Svartskataudden. 18 km SSV Kalix., Nb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>870093</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7311630</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2012-07-29</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2012-07-29</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>I myr</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>132724042</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92366</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Skagsudde, Nb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>870261</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7311655</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
